--- a/artfynd/A 51297-2024 artfynd.xlsx
+++ b/artfynd/A 51297-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5713,6 +5713,132 @@
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>23302483</v>
+      </c>
+      <c r="B41" t="n">
+        <v>56683</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100038</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Skogsduva</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Columba oenas</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Degermossen, Skogstibble skjutfält, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>628205</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6631128</v>
+      </c>
+      <c r="S41" t="n">
+        <v>419</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2005-03-26</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2005-03-28</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Upplands Rapportkommitté</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jerker Mathson, Michael Åkerberg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51297-2024 artfynd.xlsx
+++ b/artfynd/A 51297-2024 artfynd.xlsx
@@ -5718,7 +5718,7 @@
         <v>23302483</v>
       </c>
       <c r="B41" t="n">
-        <v>56683</v>
+        <v>56688</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>

--- a/artfynd/A 51297-2024 artfynd.xlsx
+++ b/artfynd/A 51297-2024 artfynd.xlsx
@@ -5733,11 +5733,6 @@
       <c r="E41" t="n">
         <v>100038</v>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Skogsduva</t>
-        </is>
-      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>Columba oenas</t>

--- a/artfynd/A 51297-2024 artfynd.xlsx
+++ b/artfynd/A 51297-2024 artfynd.xlsx
@@ -5718,7 +5718,7 @@
         <v>23302483</v>
       </c>
       <c r="B41" t="n">
-        <v>56688</v>
+        <v>56692</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5732,6 +5732,11 @@
       </c>
       <c r="E41" t="n">
         <v>100038</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Skogsduva</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>

--- a/artfynd/A 51297-2024 artfynd.xlsx
+++ b/artfynd/A 51297-2024 artfynd.xlsx
@@ -5718,7 +5718,7 @@
         <v>23302483</v>
       </c>
       <c r="B41" t="n">
-        <v>56692</v>
+        <v>56693</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>

--- a/artfynd/A 51297-2024 artfynd.xlsx
+++ b/artfynd/A 51297-2024 artfynd.xlsx
@@ -5841,10 +5841,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124286778</v>
+        <v>124286768</v>
       </c>
       <c r="B42" t="n">
-        <v>80104</v>
+        <v>79926</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5853,38 +5853,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228430</v>
+        <v>6463</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rostorangelav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Blastenia ferruginea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Huds.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>629196</v>
+        <v>628884</v>
       </c>
       <c r="R42" t="n">
-        <v>6630570</v>
+        <v>6631205</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5921,7 +5930,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm.</t>
+          <t>1 dm2 på barken på asplåga, omkr. 183 cm.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5935,7 +5944,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Äldre barr-/blandskog med mycket död gran.</t>
+          <t>Medelåldrig blandskog med överståndare.</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -5950,7 +5959,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm. # Populus tremula</t>
+          <t>Bark på stammen av asplåga, omkr. 183 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5968,10 +5977,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124286770</v>
+        <v>124286773</v>
       </c>
       <c r="B43" t="n">
-        <v>80104</v>
+        <v>79190</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5980,25 +5989,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228430</v>
+        <v>6431</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rostorangelav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Blastenia ferruginea</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Huds.) A.Massal.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6008,10 +6017,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628939</v>
+        <v>629168</v>
       </c>
       <c r="R43" t="n">
-        <v>6631046</v>
+        <v>6630544</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6048,7 +6057,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm.</t>
+          <t>På levnade asp, omkr. 207 cm.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6062,7 +6071,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Medelåldrig blandskog med överståndare.</t>
+          <t>Äldre blandskog.</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6077,7 +6086,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm. # Populus tremula</t>
+          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6095,10 +6104,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124286775</v>
+        <v>124286770</v>
       </c>
       <c r="B44" t="n">
-        <v>79920</v>
+        <v>80104</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6107,47 +6116,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>228430</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rostorangelav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Blastenia ferruginea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Huds.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>629168</v>
+        <v>628939</v>
       </c>
       <c r="R44" t="n">
-        <v>6630544</v>
+        <v>6631046</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>5 cm2 på levnade asp, omkr. 207 cm.</t>
+          <t>På bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Äldre blandskog.</t>
+          <t>Medelåldrig blandskog med överståndare.</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
+          <t>Bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6231,10 +6231,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124286769</v>
+        <v>124286781</v>
       </c>
       <c r="B45" t="n">
-        <v>6672</v>
+        <v>5361</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6243,45 +6243,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100763</v>
+        <v>101728</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cinnoberbagge</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cucujus cinnaberinus</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+          <t>(Pallas, 1773)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6290,10 +6276,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>628884</v>
+        <v>628826</v>
       </c>
       <c r="R45" t="n">
-        <v>6631205</v>
+        <v>6630334</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6330,7 +6316,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>1 larv under barken på asplåga, omkr. 183 cm.</t>
+          <t>Färska puppkamrar (ingångshål tilltäppta med ljusa, grova vedspånor) i asphögstubbe, omkr. 137 cm.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6344,7 +6330,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Medelåldrig blandskog med överståndare.</t>
+          <t>Äldre blandskog där granarna har dött.</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -6377,10 +6363,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124286781</v>
+        <v>124286780</v>
       </c>
       <c r="B46" t="n">
-        <v>5361</v>
+        <v>6672</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6389,31 +6375,45 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>101728</v>
+        <v>100763</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Cinnoberbagge</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Cucujus cinnaberinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska puppkamrar (ingångshål tilltäppta med ljusa, grova vedspånor) i asphögstubbe, omkr. 137 cm.</t>
+          <t>1 larv under barken på asphögstubbe, omkr. 137 cm.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6509,10 +6509,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124286768</v>
+        <v>124286778</v>
       </c>
       <c r="B47" t="n">
-        <v>79926</v>
+        <v>80104</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6521,47 +6521,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6463</v>
+        <v>228430</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rostorangelav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Blastenia ferruginea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Huds.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628884</v>
+        <v>629196</v>
       </c>
       <c r="R47" t="n">
-        <v>6631205</v>
+        <v>6630570</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6598,7 +6589,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>1 dm2 på barken på asplåga, omkr. 183 cm.</t>
+          <t>På bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6612,7 +6603,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Medelåldrig blandskog med överståndare.</t>
+          <t>Äldre barr-/blandskog med mycket död gran.</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -6627,7 +6618,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark på stammen av asplåga, omkr. 183 cm. # Populus tremula</t>
+          <t>Bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6645,10 +6636,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124286776</v>
+        <v>124286769</v>
       </c>
       <c r="B48" t="n">
-        <v>95551</v>
+        <v>6672</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6657,35 +6648,45 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>210</v>
+        <v>100763</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Cinnoberbagge</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Cucujus cinnaberinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6694,10 +6695,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>629163</v>
+        <v>628884</v>
       </c>
       <c r="R48" t="n">
-        <v>6630553</v>
+        <v>6631205</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6734,7 +6735,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>3 kapslar på starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm.</t>
+          <t>1 larv under barken på asplåga, omkr. 183 cm.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6748,22 +6749,22 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Äldre blandskog.</t>
+          <t>Medelåldrig blandskog med överståndare.</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm. # Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6781,10 +6782,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124286773</v>
+        <v>124286775</v>
       </c>
       <c r="B49" t="n">
-        <v>79190</v>
+        <v>79920</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6797,24 +6798,33 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6431</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
@@ -6861,7 +6871,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På levnade asp, omkr. 207 cm.</t>
+          <t>5 cm2 på levnade asp, omkr. 207 cm.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6908,10 +6918,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124286780</v>
+        <v>124286776</v>
       </c>
       <c r="B50" t="n">
-        <v>6672</v>
+        <v>95551</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6920,45 +6930,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100763</v>
+        <v>210</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cinnoberbagge</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cucujus cinnaberinus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6967,10 +6967,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628826</v>
+        <v>629163</v>
       </c>
       <c r="R50" t="n">
-        <v>6630334</v>
+        <v>6630553</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>1 larv under barken på asphögstubbe, omkr. 137 cm.</t>
+          <t>3 kapslar på starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7021,22 +7021,22 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Äldre blandskog där granarna har dött.</t>
+          <t>Äldre blandskog.</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm. # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>

--- a/artfynd/A 51297-2024 artfynd.xlsx
+++ b/artfynd/A 51297-2024 artfynd.xlsx
@@ -5841,10 +5841,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124286768</v>
+        <v>124286773</v>
       </c>
       <c r="B42" t="n">
-        <v>79926</v>
+        <v>79190</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5857,43 +5857,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6463</v>
+        <v>6431</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628884</v>
+        <v>629168</v>
       </c>
       <c r="R42" t="n">
-        <v>6631205</v>
+        <v>6630544</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5930,7 +5921,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>1 dm2 på barken på asplåga, omkr. 183 cm.</t>
+          <t>På levnade asp, omkr. 207 cm.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5944,7 +5935,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Medelåldrig blandskog med överståndare.</t>
+          <t>Äldre blandskog.</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -5959,7 +5950,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark på stammen av asplåga, omkr. 183 cm. # Populus tremula</t>
+          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5977,10 +5968,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124286773</v>
+        <v>124286770</v>
       </c>
       <c r="B43" t="n">
-        <v>79190</v>
+        <v>80104</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5989,25 +5980,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6431</v>
+        <v>228430</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Rostorangelav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Blastenia ferruginea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Huds.) A.Massal.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6017,10 +6008,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>629168</v>
+        <v>628939</v>
       </c>
       <c r="R43" t="n">
-        <v>6630544</v>
+        <v>6631046</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6057,7 +6048,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På levnade asp, omkr. 207 cm.</t>
+          <t>På bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6071,7 +6062,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Äldre blandskog.</t>
+          <t>Medelåldrig blandskog med överståndare.</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6086,7 +6077,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
+          <t>Bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6104,10 +6095,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124286770</v>
+        <v>124286769</v>
       </c>
       <c r="B44" t="n">
-        <v>80104</v>
+        <v>6672</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6116,38 +6107,57 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228430</v>
+        <v>100763</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rostorangelav</t>
+          <t>Cinnoberbagge</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Blastenia ferruginea</t>
+          <t>Cucujus cinnaberinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Huds.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>628939</v>
+        <v>628884</v>
       </c>
       <c r="R44" t="n">
-        <v>6631046</v>
+        <v>6631205</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6184,7 +6194,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm.</t>
+          <t>1 larv under barken på asplåga, omkr. 183 cm.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6213,7 +6223,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm. # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6231,10 +6241,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124286781</v>
+        <v>124286776</v>
       </c>
       <c r="B45" t="n">
-        <v>5361</v>
+        <v>95551</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6243,31 +6253,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>101728</v>
+        <v>210</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6276,10 +6290,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>628826</v>
+        <v>629163</v>
       </c>
       <c r="R45" t="n">
-        <v>6630334</v>
+        <v>6630553</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6316,7 +6330,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Färska puppkamrar (ingångshål tilltäppta med ljusa, grova vedspånor) i asphögstubbe, omkr. 137 cm.</t>
+          <t>3 kapslar på starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6330,22 +6344,22 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Äldre blandskog där granarna har dött.</t>
+          <t>Äldre blandskog.</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm. # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6363,10 +6377,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124286780</v>
+        <v>124286781</v>
       </c>
       <c r="B46" t="n">
-        <v>6672</v>
+        <v>5361</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6375,45 +6389,31 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100763</v>
+        <v>101728</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cinnoberbagge</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cucujus cinnaberinus</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+          <t>(Pallas, 1773)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>1 larv under barken på asphögstubbe, omkr. 137 cm.</t>
+          <t>Färska puppkamrar (ingångshål tilltäppta med ljusa, grova vedspånor) i asphögstubbe, omkr. 137 cm.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6509,10 +6509,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124286778</v>
+        <v>124286768</v>
       </c>
       <c r="B47" t="n">
-        <v>80104</v>
+        <v>79926</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6521,38 +6521,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228430</v>
+        <v>6463</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rostorangelav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Blastenia ferruginea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Huds.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>629196</v>
+        <v>628884</v>
       </c>
       <c r="R47" t="n">
-        <v>6630570</v>
+        <v>6631205</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6589,7 +6598,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm.</t>
+          <t>1 dm2 på barken på asplåga, omkr. 183 cm.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6603,7 +6612,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Äldre barr-/blandskog med mycket död gran.</t>
+          <t>Medelåldrig blandskog med överståndare.</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -6618,7 +6627,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm. # Populus tremula</t>
+          <t>Bark på stammen av asplåga, omkr. 183 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6636,10 +6645,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124286769</v>
+        <v>124286775</v>
       </c>
       <c r="B48" t="n">
-        <v>6672</v>
+        <v>79920</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6648,45 +6657,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100763</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cinnoberbagge</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cucujus cinnaberinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6695,10 +6694,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628884</v>
+        <v>629168</v>
       </c>
       <c r="R48" t="n">
-        <v>6631205</v>
+        <v>6630544</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6735,7 +6734,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>1 larv under barken på asplåga, omkr. 183 cm.</t>
+          <t>5 cm2 på levnade asp, omkr. 207 cm.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6749,7 +6748,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Medelåldrig blandskog med överståndare.</t>
+          <t>Äldre blandskog.</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -6764,7 +6763,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6782,10 +6781,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124286775</v>
+        <v>124286778</v>
       </c>
       <c r="B49" t="n">
-        <v>79920</v>
+        <v>80104</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6794,47 +6793,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>228430</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rostorangelav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Blastenia ferruginea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Huds.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>629168</v>
+        <v>629196</v>
       </c>
       <c r="R49" t="n">
-        <v>6630544</v>
+        <v>6630570</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6871,7 +6861,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>5 cm2 på levnade asp, omkr. 207 cm.</t>
+          <t>På bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6885,7 +6875,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Äldre blandskog.</t>
+          <t>Äldre barr-/blandskog med mycket död gran.</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -6900,7 +6890,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
+          <t>Bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6918,10 +6908,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124286776</v>
+        <v>124286780</v>
       </c>
       <c r="B50" t="n">
-        <v>95551</v>
+        <v>6672</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6930,35 +6920,45 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>210</v>
+        <v>100763</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Cinnoberbagge</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Cucujus cinnaberinus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6967,10 +6967,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>629163</v>
+        <v>628826</v>
       </c>
       <c r="R50" t="n">
-        <v>6630553</v>
+        <v>6630334</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>3 kapslar på starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm.</t>
+          <t>1 larv under barken på asphögstubbe, omkr. 137 cm.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7021,22 +7021,22 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Äldre blandskog.</t>
+          <t>Äldre blandskog där granarna har dött.</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm. # Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>

--- a/artfynd/A 51297-2024 artfynd.xlsx
+++ b/artfynd/A 51297-2024 artfynd.xlsx
@@ -5841,10 +5841,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124286773</v>
+        <v>124286781</v>
       </c>
       <c r="B42" t="n">
-        <v>79190</v>
+        <v>5361</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5853,38 +5853,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6431</v>
+        <v>101728</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>629168</v>
+        <v>628826</v>
       </c>
       <c r="R42" t="n">
-        <v>6630544</v>
+        <v>6630334</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5921,7 +5926,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På levnade asp, omkr. 207 cm.</t>
+          <t>Färska puppkamrar (ingångshål tilltäppta med ljusa, grova vedspånor) i asphögstubbe, omkr. 137 cm.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5935,7 +5940,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Äldre blandskog.</t>
+          <t>Äldre blandskog där granarna har dött.</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -5950,7 +5955,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5968,10 +5973,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124286770</v>
+        <v>124286776</v>
       </c>
       <c r="B43" t="n">
-        <v>80104</v>
+        <v>95551</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5980,38 +5985,47 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228430</v>
+        <v>210</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rostorangelav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Blastenia ferruginea</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Huds.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628939</v>
+        <v>629163</v>
       </c>
       <c r="R43" t="n">
-        <v>6631046</v>
+        <v>6630553</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6048,7 +6062,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm.</t>
+          <t>3 kapslar på starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6062,22 +6076,22 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Medelåldrig blandskog med överståndare.</t>
+          <t>Äldre blandskog.</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm. # Populus tremula</t>
+          <t>Starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm. # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6095,7 +6109,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124286769</v>
+        <v>124286780</v>
       </c>
       <c r="B44" t="n">
         <v>6672</v>
@@ -6154,10 +6168,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>628884</v>
+        <v>628826</v>
       </c>
       <c r="R44" t="n">
-        <v>6631205</v>
+        <v>6630334</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6194,7 +6208,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>1 larv under barken på asplåga, omkr. 183 cm.</t>
+          <t>1 larv under barken på asphögstubbe, omkr. 137 cm.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6208,7 +6222,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Medelåldrig blandskog med överståndare.</t>
+          <t>Äldre blandskog där granarna har dött.</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -6241,10 +6255,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124286776</v>
+        <v>124286775</v>
       </c>
       <c r="B45" t="n">
-        <v>95551</v>
+        <v>79920</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6257,31 +6271,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>210</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6290,10 +6304,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>629163</v>
+        <v>629168</v>
       </c>
       <c r="R45" t="n">
-        <v>6630553</v>
+        <v>6630544</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6330,7 +6344,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>3 kapslar på starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm.</t>
+          <t>5 cm2 på levnade asp, omkr. 207 cm.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6349,17 +6363,17 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm. # Picea abies</t>
+          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6377,10 +6391,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124286781</v>
+        <v>124286778</v>
       </c>
       <c r="B46" t="n">
-        <v>5361</v>
+        <v>80104</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6389,43 +6403,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>101728</v>
+        <v>228430</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Rostorangelav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Blastenia ferruginea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Huds.) A.Massal.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>628826</v>
+        <v>629196</v>
       </c>
       <c r="R46" t="n">
-        <v>6630334</v>
+        <v>6630570</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6462,7 +6471,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska puppkamrar (ingångshål tilltäppta med ljusa, grova vedspånor) i asphögstubbe, omkr. 137 cm.</t>
+          <t>På bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6476,7 +6485,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Äldre blandskog där granarna har dött.</t>
+          <t>Äldre barr-/blandskog med mycket död gran.</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -6491,7 +6500,7 @@
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6509,10 +6518,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124286768</v>
+        <v>124286769</v>
       </c>
       <c r="B47" t="n">
-        <v>79926</v>
+        <v>6672</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6521,25 +6530,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6463</v>
+        <v>100763</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Cinnoberbagge</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cucujus cinnaberinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -6547,9 +6556,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>dm²</t>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6598,7 +6617,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>1 dm2 på barken på asplåga, omkr. 183 cm.</t>
+          <t>1 larv under barken på asplåga, omkr. 183 cm.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6627,7 +6646,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark på stammen av asplåga, omkr. 183 cm. # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6645,10 +6664,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124286775</v>
+        <v>124286770</v>
       </c>
       <c r="B48" t="n">
-        <v>79920</v>
+        <v>80104</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6657,47 +6676,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>228430</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rostorangelav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Blastenia ferruginea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Huds.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>629168</v>
+        <v>628939</v>
       </c>
       <c r="R48" t="n">
-        <v>6630544</v>
+        <v>6631046</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6734,7 +6744,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>5 cm2 på levnade asp, omkr. 207 cm.</t>
+          <t>På bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6748,7 +6758,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Äldre blandskog.</t>
+          <t>Medelåldrig blandskog med överståndare.</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -6763,7 +6773,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
+          <t>Bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6781,10 +6791,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124286778</v>
+        <v>124286768</v>
       </c>
       <c r="B49" t="n">
-        <v>80104</v>
+        <v>79926</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6793,38 +6803,47 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228430</v>
+        <v>6463</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rostorangelav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Blastenia ferruginea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Huds.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>629196</v>
+        <v>628884</v>
       </c>
       <c r="R49" t="n">
-        <v>6630570</v>
+        <v>6631205</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6861,7 +6880,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm.</t>
+          <t>1 dm2 på barken på asplåga, omkr. 183 cm.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6875,7 +6894,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Äldre barr-/blandskog med mycket död gran.</t>
+          <t>Medelåldrig blandskog med överståndare.</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -6890,7 +6909,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm. # Populus tremula</t>
+          <t>Bark på stammen av asplåga, omkr. 183 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6908,10 +6927,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124286780</v>
+        <v>124286773</v>
       </c>
       <c r="B50" t="n">
-        <v>6672</v>
+        <v>79190</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6920,57 +6939,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100763</v>
+        <v>6431</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cinnoberbagge</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cucujus cinnaberinus</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628826</v>
+        <v>629168</v>
       </c>
       <c r="R50" t="n">
-        <v>6630334</v>
+        <v>6630544</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>1 larv under barken på asphögstubbe, omkr. 137 cm.</t>
+          <t>På levnade asp, omkr. 207 cm.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Äldre blandskog där granarna har dött.</t>
+          <t>Äldre blandskog.</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>

--- a/artfynd/A 51297-2024 artfynd.xlsx
+++ b/artfynd/A 51297-2024 artfynd.xlsx
@@ -5841,10 +5841,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124286781</v>
+        <v>124286768</v>
       </c>
       <c r="B42" t="n">
-        <v>5361</v>
+        <v>79926</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5853,31 +5853,35 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>101728</v>
+        <v>6463</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5886,10 +5890,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628826</v>
+        <v>628884</v>
       </c>
       <c r="R42" t="n">
-        <v>6630334</v>
+        <v>6631205</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5926,7 +5930,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färska puppkamrar (ingångshål tilltäppta med ljusa, grova vedspånor) i asphögstubbe, omkr. 137 cm.</t>
+          <t>1 dm2 på barken på asplåga, omkr. 183 cm.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5940,7 +5944,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Äldre blandskog där granarna har dött.</t>
+          <t>Medelåldrig blandskog med överståndare.</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -5955,7 +5959,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Bark på stammen av asplåga, omkr. 183 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5973,10 +5977,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124286776</v>
+        <v>124286769</v>
       </c>
       <c r="B43" t="n">
-        <v>95551</v>
+        <v>6672</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5985,35 +5989,45 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>210</v>
+        <v>100763</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Cinnoberbagge</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Cucujus cinnaberinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -6022,10 +6036,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>629163</v>
+        <v>628884</v>
       </c>
       <c r="R43" t="n">
-        <v>6630553</v>
+        <v>6631205</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6062,7 +6076,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>3 kapslar på starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm.</t>
+          <t>1 larv under barken på asplåga, omkr. 183 cm.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6076,22 +6090,22 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Äldre blandskog.</t>
+          <t>Medelåldrig blandskog med överståndare.</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm. # Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6109,10 +6123,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124286780</v>
+        <v>124286775</v>
       </c>
       <c r="B44" t="n">
-        <v>6672</v>
+        <v>79920</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6121,45 +6135,35 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100763</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cinnoberbagge</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cucujus cinnaberinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6168,10 +6172,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>628826</v>
+        <v>629168</v>
       </c>
       <c r="R44" t="n">
-        <v>6630334</v>
+        <v>6630544</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6208,7 +6212,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>1 larv under barken på asphögstubbe, omkr. 137 cm.</t>
+          <t>5 cm2 på levnade asp, omkr. 207 cm.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6222,7 +6226,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Äldre blandskog där granarna har dött.</t>
+          <t>Äldre blandskog.</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -6237,7 +6241,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6255,10 +6259,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124286775</v>
+        <v>124286778</v>
       </c>
       <c r="B45" t="n">
-        <v>79920</v>
+        <v>80104</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6267,47 +6271,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>228430</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rostorangelav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Blastenia ferruginea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Huds.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>629168</v>
+        <v>629196</v>
       </c>
       <c r="R45" t="n">
-        <v>6630544</v>
+        <v>6630570</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6344,7 +6339,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>5 cm2 på levnade asp, omkr. 207 cm.</t>
+          <t>På bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6358,7 +6353,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Äldre blandskog.</t>
+          <t>Äldre barr-/blandskog med mycket död gran.</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -6373,7 +6368,7 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
+          <t>Bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6391,10 +6386,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124286778</v>
+        <v>124286773</v>
       </c>
       <c r="B46" t="n">
-        <v>80104</v>
+        <v>79190</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6403,25 +6398,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228430</v>
+        <v>6431</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rostorangelav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Blastenia ferruginea</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Huds.) A.Massal.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6431,10 +6426,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>629196</v>
+        <v>629168</v>
       </c>
       <c r="R46" t="n">
-        <v>6630570</v>
+        <v>6630544</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6471,7 +6466,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm.</t>
+          <t>På levnade asp, omkr. 207 cm.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6485,7 +6480,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Äldre barr-/blandskog med mycket död gran.</t>
+          <t>Äldre blandskog.</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -6500,7 +6495,7 @@
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm. # Populus tremula</t>
+          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6518,7 +6513,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124286769</v>
+        <v>124286780</v>
       </c>
       <c r="B47" t="n">
         <v>6672</v>
@@ -6577,10 +6572,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628884</v>
+        <v>628826</v>
       </c>
       <c r="R47" t="n">
-        <v>6631205</v>
+        <v>6630334</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6617,7 +6612,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>1 larv under barken på asplåga, omkr. 183 cm.</t>
+          <t>1 larv under barken på asphögstubbe, omkr. 137 cm.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6631,7 +6626,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Medelåldrig blandskog med överståndare.</t>
+          <t>Äldre blandskog där granarna har dött.</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -6664,10 +6659,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124286770</v>
+        <v>124286781</v>
       </c>
       <c r="B48" t="n">
-        <v>80104</v>
+        <v>5361</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6676,38 +6671,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228430</v>
+        <v>101728</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rostorangelav</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Blastenia ferruginea</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Huds.) A.Massal.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628939</v>
+        <v>628826</v>
       </c>
       <c r="R48" t="n">
-        <v>6631046</v>
+        <v>6630334</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm.</t>
+          <t>Färska puppkamrar (ingångshål tilltäppta med ljusa, grova vedspånor) i asphögstubbe, omkr. 137 cm.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Medelåldrig blandskog med överståndare.</t>
+          <t>Äldre blandskog där granarna har dött.</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm. # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6791,10 +6791,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124286768</v>
+        <v>124286770</v>
       </c>
       <c r="B49" t="n">
-        <v>79926</v>
+        <v>80104</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6803,47 +6803,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6463</v>
+        <v>228430</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rostorangelav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Blastenia ferruginea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Huds.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628884</v>
+        <v>628939</v>
       </c>
       <c r="R49" t="n">
-        <v>6631205</v>
+        <v>6631046</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6880,7 +6871,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>1 dm2 på barken på asplåga, omkr. 183 cm.</t>
+          <t>På bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6909,7 +6900,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Bark på stammen av asplåga, omkr. 183 cm. # Populus tremula</t>
+          <t>Bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6927,10 +6918,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124286773</v>
+        <v>124286776</v>
       </c>
       <c r="B50" t="n">
-        <v>79190</v>
+        <v>95551</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6943,34 +6934,43 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6431</v>
+        <v>210</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>629168</v>
+        <v>629163</v>
       </c>
       <c r="R50" t="n">
-        <v>6630544</v>
+        <v>6630553</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På levnade asp, omkr. 207 cm.</t>
+          <t>3 kapslar på starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7026,17 +7026,17 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
+          <t>Starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm. # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>

--- a/artfynd/A 51297-2024 artfynd.xlsx
+++ b/artfynd/A 51297-2024 artfynd.xlsx
@@ -5841,10 +5841,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124286768</v>
+        <v>124286769</v>
       </c>
       <c r="B42" t="n">
-        <v>79926</v>
+        <v>6672</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5853,25 +5853,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6463</v>
+        <v>100763</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Cinnoberbagge</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cucujus cinnaberinus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5879,9 +5879,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>dm²</t>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5930,7 +5940,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>1 dm2 på barken på asplåga, omkr. 183 cm.</t>
+          <t>1 larv under barken på asplåga, omkr. 183 cm.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5959,7 +5969,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark på stammen av asplåga, omkr. 183 cm. # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5977,10 +5987,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124286769</v>
+        <v>124286768</v>
       </c>
       <c r="B43" t="n">
-        <v>6672</v>
+        <v>79926</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5989,25 +5999,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100763</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cinnoberbagge</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cucujus cinnaberinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -6015,19 +6025,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>1 larv under barken på asplåga, omkr. 183 cm.</t>
+          <t>1 dm2 på barken på asplåga, omkr. 183 cm.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Bark på stammen av asplåga, omkr. 183 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 51297-2024 artfynd.xlsx
+++ b/artfynd/A 51297-2024 artfynd.xlsx
@@ -5841,10 +5841,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124286769</v>
+        <v>124286770</v>
       </c>
       <c r="B42" t="n">
-        <v>6672</v>
+        <v>80104</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5853,57 +5853,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100763</v>
+        <v>228430</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cinnoberbagge</t>
+          <t>Rostorangelav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cucujus cinnaberinus</t>
+          <t>Blastenia ferruginea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Huds.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628884</v>
+        <v>628939</v>
       </c>
       <c r="R42" t="n">
-        <v>6631205</v>
+        <v>6631046</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5940,7 +5921,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>1 larv under barken på asplåga, omkr. 183 cm.</t>
+          <t>På bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5969,7 +5950,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5987,10 +5968,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124286768</v>
+        <v>124286769</v>
       </c>
       <c r="B43" t="n">
-        <v>79926</v>
+        <v>6672</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5999,25 +5980,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>100763</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Cinnoberbagge</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cucujus cinnaberinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -6025,9 +6006,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>dm²</t>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -6076,7 +6067,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>1 dm2 på barken på asplåga, omkr. 183 cm.</t>
+          <t>1 larv under barken på asplåga, omkr. 183 cm.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6105,7 +6096,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark på stammen av asplåga, omkr. 183 cm. # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6123,10 +6114,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124286775</v>
+        <v>124286773</v>
       </c>
       <c r="B44" t="n">
-        <v>79920</v>
+        <v>79190</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6139,33 +6130,24 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>6431</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
@@ -6212,7 +6194,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>5 cm2 på levnade asp, omkr. 207 cm.</t>
+          <t>På levnade asp, omkr. 207 cm.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6259,10 +6241,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124286778</v>
+        <v>124286781</v>
       </c>
       <c r="B45" t="n">
-        <v>80104</v>
+        <v>5361</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6271,38 +6253,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228430</v>
+        <v>101728</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rostorangelav</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Blastenia ferruginea</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Huds.) A.Massal.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>629196</v>
+        <v>628826</v>
       </c>
       <c r="R45" t="n">
-        <v>6630570</v>
+        <v>6630334</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6339,7 +6326,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm.</t>
+          <t>Färska puppkamrar (ingångshål tilltäppta med ljusa, grova vedspånor) i asphögstubbe, omkr. 137 cm.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6353,7 +6340,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Äldre barr-/blandskog med mycket död gran.</t>
+          <t>Äldre blandskog där granarna har dött.</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -6368,7 +6355,7 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm. # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6386,10 +6373,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124286773</v>
+        <v>124286776</v>
       </c>
       <c r="B46" t="n">
-        <v>79190</v>
+        <v>95551</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6402,34 +6389,43 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6431</v>
+        <v>210</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>629168</v>
+        <v>629163</v>
       </c>
       <c r="R46" t="n">
-        <v>6630544</v>
+        <v>6630553</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6466,7 +6462,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På levnade asp, omkr. 207 cm.</t>
+          <t>3 kapslar på starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6485,17 +6481,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
+          <t>Starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm. # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6659,10 +6655,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124286781</v>
+        <v>124286775</v>
       </c>
       <c r="B48" t="n">
-        <v>5361</v>
+        <v>79920</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6671,31 +6667,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>101728</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6704,10 +6704,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628826</v>
+        <v>629168</v>
       </c>
       <c r="R48" t="n">
-        <v>6630334</v>
+        <v>6630544</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Färska puppkamrar (ingångshål tilltäppta med ljusa, grova vedspånor) i asphögstubbe, omkr. 137 cm.</t>
+          <t>5 cm2 på levnade asp, omkr. 207 cm.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Äldre blandskog där granarna har dött.</t>
+          <t>Äldre blandskog.</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6791,7 +6791,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124286770</v>
+        <v>124286778</v>
       </c>
       <c r="B49" t="n">
         <v>80104</v>
@@ -6831,10 +6831,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628939</v>
+        <v>629196</v>
       </c>
       <c r="R49" t="n">
-        <v>6631046</v>
+        <v>6630570</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm.</t>
+          <t>På bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Medelåldrig blandskog med överståndare.</t>
+          <t>Äldre barr-/blandskog med mycket död gran.</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm. # Populus tremula</t>
+          <t>Bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6918,10 +6918,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124286776</v>
+        <v>124286768</v>
       </c>
       <c r="B50" t="n">
-        <v>95551</v>
+        <v>79926</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6934,31 +6934,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>210</v>
+        <v>6463</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6967,10 +6967,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>629163</v>
+        <v>628884</v>
       </c>
       <c r="R50" t="n">
-        <v>6630553</v>
+        <v>6631205</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>3 kapslar på starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm.</t>
+          <t>1 dm2 på barken på asplåga, omkr. 183 cm.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7021,22 +7021,22 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Äldre blandskog.</t>
+          <t>Medelåldrig blandskog med överståndare.</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm. # Picea abies</t>
+          <t>Bark på stammen av asplåga, omkr. 183 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>

--- a/artfynd/A 51297-2024 artfynd.xlsx
+++ b/artfynd/A 51297-2024 artfynd.xlsx
@@ -5968,10 +5968,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124286769</v>
+        <v>124286773</v>
       </c>
       <c r="B43" t="n">
-        <v>6672</v>
+        <v>79190</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5980,57 +5980,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100763</v>
+        <v>6431</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cinnoberbagge</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cucujus cinnaberinus</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628884</v>
+        <v>629168</v>
       </c>
       <c r="R43" t="n">
-        <v>6631205</v>
+        <v>6630544</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6067,7 +6048,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>1 larv under barken på asplåga, omkr. 183 cm.</t>
+          <t>På levnade asp, omkr. 207 cm.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6081,7 +6062,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Medelåldrig blandskog med överståndare.</t>
+          <t>Äldre blandskog.</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6096,7 +6077,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6114,10 +6095,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124286773</v>
+        <v>124286769</v>
       </c>
       <c r="B44" t="n">
-        <v>79190</v>
+        <v>6672</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6126,38 +6107,57 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6431</v>
+        <v>100763</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Cinnoberbagge</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Cucujus cinnaberinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>629168</v>
+        <v>628884</v>
       </c>
       <c r="R44" t="n">
-        <v>6630544</v>
+        <v>6631205</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På levnade asp, omkr. 207 cm.</t>
+          <t>1 larv under barken på asplåga, omkr. 183 cm.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Äldre blandskog.</t>
+          <t>Medelåldrig blandskog med överståndare.</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>

--- a/artfynd/A 51297-2024 artfynd.xlsx
+++ b/artfynd/A 51297-2024 artfynd.xlsx
@@ -5841,10 +5841,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124286770</v>
+        <v>124286776</v>
       </c>
       <c r="B42" t="n">
-        <v>80104</v>
+        <v>95551</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5853,38 +5853,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228430</v>
+        <v>210</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rostorangelav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Blastenia ferruginea</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Huds.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628939</v>
+        <v>629163</v>
       </c>
       <c r="R42" t="n">
-        <v>6631046</v>
+        <v>6630553</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5921,7 +5930,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm.</t>
+          <t>3 kapslar på starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5935,22 +5944,22 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Medelåldrig blandskog med överståndare.</t>
+          <t>Äldre blandskog.</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm. # Populus tremula</t>
+          <t>Starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm. # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5968,10 +5977,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124286773</v>
+        <v>124286781</v>
       </c>
       <c r="B43" t="n">
-        <v>79190</v>
+        <v>5361</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5980,38 +5989,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6431</v>
+        <v>101728</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>629168</v>
+        <v>628826</v>
       </c>
       <c r="R43" t="n">
-        <v>6630544</v>
+        <v>6630334</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6048,7 +6062,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På levnade asp, omkr. 207 cm.</t>
+          <t>Färska puppkamrar (ingångshål tilltäppta med ljusa, grova vedspånor) i asphögstubbe, omkr. 137 cm.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6062,7 +6076,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Äldre blandskog.</t>
+          <t>Äldre blandskog där granarna har dött.</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6077,7 +6091,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6095,10 +6109,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124286769</v>
+        <v>124286778</v>
       </c>
       <c r="B44" t="n">
-        <v>6672</v>
+        <v>80104</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6107,57 +6121,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100763</v>
+        <v>228430</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cinnoberbagge</t>
+          <t>Rostorangelav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cucujus cinnaberinus</t>
+          <t>Blastenia ferruginea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Huds.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>628884</v>
+        <v>629196</v>
       </c>
       <c r="R44" t="n">
-        <v>6631205</v>
+        <v>6630570</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6194,7 +6189,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>1 larv under barken på asplåga, omkr. 183 cm.</t>
+          <t>På bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6208,7 +6203,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Medelåldrig blandskog med överståndare.</t>
+          <t>Äldre barr-/blandskog med mycket död gran.</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -6223,7 +6218,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6241,10 +6236,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124286781</v>
+        <v>124286768</v>
       </c>
       <c r="B45" t="n">
-        <v>5361</v>
+        <v>79926</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6253,31 +6248,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>101728</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6286,10 +6285,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>628826</v>
+        <v>628884</v>
       </c>
       <c r="R45" t="n">
-        <v>6630334</v>
+        <v>6631205</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6326,7 +6325,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Färska puppkamrar (ingångshål tilltäppta med ljusa, grova vedspånor) i asphögstubbe, omkr. 137 cm.</t>
+          <t>1 dm2 på barken på asplåga, omkr. 183 cm.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6340,7 +6339,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Äldre blandskog där granarna har dött.</t>
+          <t>Medelåldrig blandskog med överståndare.</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -6355,7 +6354,7 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Bark på stammen av asplåga, omkr. 183 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6373,10 +6372,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124286776</v>
+        <v>124286775</v>
       </c>
       <c r="B46" t="n">
-        <v>95551</v>
+        <v>79920</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6389,31 +6388,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>210</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6422,10 +6421,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>629163</v>
+        <v>629168</v>
       </c>
       <c r="R46" t="n">
-        <v>6630553</v>
+        <v>6630544</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6462,7 +6461,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>3 kapslar på starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm.</t>
+          <t>5 cm2 på levnade asp, omkr. 207 cm.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6481,17 +6480,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm. # Picea abies</t>
+          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6509,7 +6508,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124286780</v>
+        <v>124286769</v>
       </c>
       <c r="B47" t="n">
         <v>6672</v>
@@ -6568,10 +6567,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628826</v>
+        <v>628884</v>
       </c>
       <c r="R47" t="n">
-        <v>6630334</v>
+        <v>6631205</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6608,7 +6607,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>1 larv under barken på asphögstubbe, omkr. 137 cm.</t>
+          <t>1 larv under barken på asplåga, omkr. 183 cm.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6622,7 +6621,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Äldre blandskog där granarna har dött.</t>
+          <t>Medelåldrig blandskog med överståndare.</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -6655,10 +6654,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124286775</v>
+        <v>124286780</v>
       </c>
       <c r="B48" t="n">
-        <v>79920</v>
+        <v>6672</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6667,35 +6666,45 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>100763</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Cinnoberbagge</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cucujus cinnaberinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>cm²</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6704,10 +6713,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>629168</v>
+        <v>628826</v>
       </c>
       <c r="R48" t="n">
-        <v>6630544</v>
+        <v>6630334</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6744,7 +6753,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>5 cm2 på levnade asp, omkr. 207 cm.</t>
+          <t>1 larv under barken på asphögstubbe, omkr. 137 cm.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6758,7 +6767,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Äldre blandskog.</t>
+          <t>Äldre blandskog där granarna har dött.</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -6773,7 +6782,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6791,10 +6800,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124286778</v>
+        <v>124286773</v>
       </c>
       <c r="B49" t="n">
-        <v>80104</v>
+        <v>79190</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6803,25 +6812,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228430</v>
+        <v>6431</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rostorangelav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Blastenia ferruginea</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Huds.) A.Massal.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6831,10 +6840,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>629196</v>
+        <v>629168</v>
       </c>
       <c r="R49" t="n">
-        <v>6630570</v>
+        <v>6630544</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6871,7 +6880,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm.</t>
+          <t>På levnade asp, omkr. 207 cm.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6885,7 +6894,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Äldre barr-/blandskog med mycket död gran.</t>
+          <t>Äldre blandskog.</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -6900,7 +6909,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm. # Populus tremula</t>
+          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6918,10 +6927,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124286768</v>
+        <v>124286770</v>
       </c>
       <c r="B50" t="n">
-        <v>79926</v>
+        <v>80104</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6930,47 +6939,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6463</v>
+        <v>228430</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rostorangelav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Blastenia ferruginea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Huds.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628884</v>
+        <v>628939</v>
       </c>
       <c r="R50" t="n">
-        <v>6631205</v>
+        <v>6631046</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>1 dm2 på barken på asplåga, omkr. 183 cm.</t>
+          <t>På bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Bark på stammen av asplåga, omkr. 183 cm. # Populus tremula</t>
+          <t>Bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>

--- a/artfynd/A 51297-2024 artfynd.xlsx
+++ b/artfynd/A 51297-2024 artfynd.xlsx
@@ -5841,10 +5841,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124286776</v>
+        <v>124286775</v>
       </c>
       <c r="B42" t="n">
-        <v>95551</v>
+        <v>79920</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5857,31 +5857,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>210</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5890,10 +5890,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>629163</v>
+        <v>629168</v>
       </c>
       <c r="R42" t="n">
-        <v>6630553</v>
+        <v>6630544</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>3 kapslar på starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm.</t>
+          <t>5 cm2 på levnade asp, omkr. 207 cm.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5949,17 +5949,17 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm. # Picea abies</t>
+          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5977,10 +5977,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124286781</v>
+        <v>124286773</v>
       </c>
       <c r="B43" t="n">
-        <v>5361</v>
+        <v>79190</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5989,43 +5989,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>101728</v>
+        <v>6431</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628826</v>
+        <v>629168</v>
       </c>
       <c r="R43" t="n">
-        <v>6630334</v>
+        <v>6630544</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6062,7 +6057,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färska puppkamrar (ingångshål tilltäppta med ljusa, grova vedspånor) i asphögstubbe, omkr. 137 cm.</t>
+          <t>På levnade asp, omkr. 207 cm.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6076,7 +6071,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Äldre blandskog där granarna har dött.</t>
+          <t>Äldre blandskog.</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6091,7 +6086,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6109,7 +6104,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124286778</v>
+        <v>124286770</v>
       </c>
       <c r="B44" t="n">
         <v>80104</v>
@@ -6149,10 +6144,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>629196</v>
+        <v>628939</v>
       </c>
       <c r="R44" t="n">
-        <v>6630570</v>
+        <v>6631046</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6189,7 +6184,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm.</t>
+          <t>På bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6203,7 +6198,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Äldre barr-/blandskog med mycket död gran.</t>
+          <t>Medelåldrig blandskog med överståndare.</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -6218,7 +6213,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm. # Populus tremula</t>
+          <t>Bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6372,10 +6367,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124286775</v>
+        <v>124286776</v>
       </c>
       <c r="B46" t="n">
-        <v>79920</v>
+        <v>95551</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6388,31 +6383,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>210</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6421,10 +6416,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>629168</v>
+        <v>629163</v>
       </c>
       <c r="R46" t="n">
-        <v>6630544</v>
+        <v>6630553</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6461,7 +6456,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>5 cm2 på levnade asp, omkr. 207 cm.</t>
+          <t>3 kapslar på starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6480,17 +6475,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
+          <t>Starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm. # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6800,10 +6795,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124286773</v>
+        <v>124286778</v>
       </c>
       <c r="B49" t="n">
-        <v>79190</v>
+        <v>80104</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6812,25 +6807,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6431</v>
+        <v>228430</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Rostorangelav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Blastenia ferruginea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Huds.) A.Massal.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6840,10 +6835,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>629168</v>
+        <v>629196</v>
       </c>
       <c r="R49" t="n">
-        <v>6630544</v>
+        <v>6630570</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6880,7 +6875,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På levnade asp, omkr. 207 cm.</t>
+          <t>På bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6894,7 +6889,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Äldre blandskog.</t>
+          <t>Äldre barr-/blandskog med mycket död gran.</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -6909,7 +6904,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
+          <t>Bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6927,10 +6922,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124286770</v>
+        <v>124286781</v>
       </c>
       <c r="B50" t="n">
-        <v>80104</v>
+        <v>5361</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6939,38 +6934,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228430</v>
+        <v>101728</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rostorangelav</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Blastenia ferruginea</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Huds.) A.Massal.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628939</v>
+        <v>628826</v>
       </c>
       <c r="R50" t="n">
-        <v>6631046</v>
+        <v>6630334</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm.</t>
+          <t>Färska puppkamrar (ingångshål tilltäppta med ljusa, grova vedspånor) i asphögstubbe, omkr. 137 cm.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Medelåldrig blandskog med överståndare.</t>
+          <t>Äldre blandskog där granarna har dött.</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm. # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>

--- a/artfynd/A 51297-2024 artfynd.xlsx
+++ b/artfynd/A 51297-2024 artfynd.xlsx
@@ -5841,10 +5841,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124286775</v>
+        <v>124286776</v>
       </c>
       <c r="B42" t="n">
-        <v>79920</v>
+        <v>95551</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5857,31 +5857,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>210</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5890,10 +5890,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>629168</v>
+        <v>629163</v>
       </c>
       <c r="R42" t="n">
-        <v>6630544</v>
+        <v>6630553</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>5 cm2 på levnade asp, omkr. 207 cm.</t>
+          <t>3 kapslar på starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5949,17 +5949,17 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
+          <t>Starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm. # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5977,10 +5977,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124286773</v>
+        <v>124286778</v>
       </c>
       <c r="B43" t="n">
-        <v>79190</v>
+        <v>80104</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5989,25 +5989,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6431</v>
+        <v>228430</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Rostorangelav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Blastenia ferruginea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Huds.) A.Massal.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6017,10 +6017,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>629168</v>
+        <v>629196</v>
       </c>
       <c r="R43" t="n">
-        <v>6630544</v>
+        <v>6630570</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6057,7 +6057,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På levnade asp, omkr. 207 cm.</t>
+          <t>På bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6071,7 +6071,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Äldre blandskog.</t>
+          <t>Äldre barr-/blandskog med mycket död gran.</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
+          <t>Bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6104,10 +6104,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124286770</v>
+        <v>124286773</v>
       </c>
       <c r="B44" t="n">
-        <v>80104</v>
+        <v>79190</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6116,25 +6116,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228430</v>
+        <v>6431</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rostorangelav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Blastenia ferruginea</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Huds.) A.Massal.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6144,10 +6144,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>628939</v>
+        <v>629168</v>
       </c>
       <c r="R44" t="n">
-        <v>6631046</v>
+        <v>6630544</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm.</t>
+          <t>På levnade asp, omkr. 207 cm.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Medelåldrig blandskog med överståndare.</t>
+          <t>Äldre blandskog.</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm. # Populus tremula</t>
+          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6367,10 +6367,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124286776</v>
+        <v>124286770</v>
       </c>
       <c r="B46" t="n">
-        <v>95551</v>
+        <v>80104</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6379,47 +6379,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>210</v>
+        <v>228430</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Rostorangelav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Blastenia ferruginea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Huds.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>629163</v>
+        <v>628939</v>
       </c>
       <c r="R46" t="n">
-        <v>6630553</v>
+        <v>6631046</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6456,7 +6447,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>3 kapslar på starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm.</t>
+          <t>På bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6470,22 +6461,22 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Äldre blandskog.</t>
+          <t>Medelåldrig blandskog med överståndare.</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm. # Picea abies</t>
+          <t>Bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6503,10 +6494,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124286769</v>
+        <v>124286775</v>
       </c>
       <c r="B47" t="n">
-        <v>6672</v>
+        <v>79920</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6515,45 +6506,35 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100763</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cinnoberbagge</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cucujus cinnaberinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6562,10 +6543,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628884</v>
+        <v>629168</v>
       </c>
       <c r="R47" t="n">
-        <v>6631205</v>
+        <v>6630544</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6602,7 +6583,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>1 larv under barken på asplåga, omkr. 183 cm.</t>
+          <t>5 cm2 på levnade asp, omkr. 207 cm.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6616,7 +6597,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Medelåldrig blandskog med överståndare.</t>
+          <t>Äldre blandskog.</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -6631,7 +6612,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6649,7 +6630,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124286780</v>
+        <v>124286769</v>
       </c>
       <c r="B48" t="n">
         <v>6672</v>
@@ -6708,10 +6689,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628826</v>
+        <v>628884</v>
       </c>
       <c r="R48" t="n">
-        <v>6630334</v>
+        <v>6631205</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6748,7 +6729,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>1 larv under barken på asphögstubbe, omkr. 137 cm.</t>
+          <t>1 larv under barken på asplåga, omkr. 183 cm.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6762,7 +6743,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Äldre blandskog där granarna har dött.</t>
+          <t>Medelåldrig blandskog med överståndare.</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -6795,10 +6776,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124286778</v>
+        <v>124286781</v>
       </c>
       <c r="B49" t="n">
-        <v>80104</v>
+        <v>5361</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6807,38 +6788,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228430</v>
+        <v>101728</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rostorangelav</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Blastenia ferruginea</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Huds.) A.Massal.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>629196</v>
+        <v>628826</v>
       </c>
       <c r="R49" t="n">
-        <v>6630570</v>
+        <v>6630334</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6875,7 +6861,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm.</t>
+          <t>Färska puppkamrar (ingångshål tilltäppta med ljusa, grova vedspånor) i asphögstubbe, omkr. 137 cm.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6889,7 +6875,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Äldre barr-/blandskog med mycket död gran.</t>
+          <t>Äldre blandskog där granarna har dött.</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -6904,7 +6890,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm. # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6922,10 +6908,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124286781</v>
+        <v>124286780</v>
       </c>
       <c r="B50" t="n">
-        <v>5361</v>
+        <v>6672</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6934,31 +6920,45 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>101728</v>
+        <v>100763</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Cinnoberbagge</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Cucujus cinnaberinus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Färska puppkamrar (ingångshål tilltäppta med ljusa, grova vedspånor) i asphögstubbe, omkr. 137 cm.</t>
+          <t>1 larv under barken på asphögstubbe, omkr. 137 cm.</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 51297-2024 artfynd.xlsx
+++ b/artfynd/A 51297-2024 artfynd.xlsx
@@ -5841,10 +5841,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124286776</v>
+        <v>124286769</v>
       </c>
       <c r="B42" t="n">
-        <v>95551</v>
+        <v>6672</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5853,35 +5853,45 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>210</v>
+        <v>100763</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Cinnoberbagge</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Cucujus cinnaberinus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5890,10 +5900,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>629163</v>
+        <v>628884</v>
       </c>
       <c r="R42" t="n">
-        <v>6630553</v>
+        <v>6631205</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5930,7 +5940,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>3 kapslar på starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm.</t>
+          <t>1 larv under barken på asplåga, omkr. 183 cm.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5944,22 +5954,22 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Äldre blandskog.</t>
+          <t>Medelåldrig blandskog med överståndare.</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm. # Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5977,10 +5987,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124286778</v>
+        <v>124286781</v>
       </c>
       <c r="B43" t="n">
-        <v>80104</v>
+        <v>5361</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5989,38 +5999,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228430</v>
+        <v>101728</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rostorangelav</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Blastenia ferruginea</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Huds.) A.Massal.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>629196</v>
+        <v>628826</v>
       </c>
       <c r="R43" t="n">
-        <v>6630570</v>
+        <v>6630334</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6057,7 +6072,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm.</t>
+          <t>Färska puppkamrar (ingångshål tilltäppta med ljusa, grova vedspånor) i asphögstubbe, omkr. 137 cm.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6071,7 +6086,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Äldre barr-/blandskog med mycket död gran.</t>
+          <t>Äldre blandskog där granarna har dött.</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6086,7 +6101,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm. # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6104,10 +6119,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124286773</v>
+        <v>124286778</v>
       </c>
       <c r="B44" t="n">
-        <v>79190</v>
+        <v>80104</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6116,25 +6131,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6431</v>
+        <v>228430</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Rostorangelav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Blastenia ferruginea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Huds.) A.Massal.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6144,10 +6159,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>629168</v>
+        <v>629196</v>
       </c>
       <c r="R44" t="n">
-        <v>6630544</v>
+        <v>6630570</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6184,7 +6199,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På levnade asp, omkr. 207 cm.</t>
+          <t>På bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6198,7 +6213,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Äldre blandskog.</t>
+          <t>Äldre barr-/blandskog med mycket död gran.</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -6213,7 +6228,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
+          <t>Bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6231,10 +6246,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124286768</v>
+        <v>124286773</v>
       </c>
       <c r="B45" t="n">
-        <v>79926</v>
+        <v>79190</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6247,43 +6262,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6463</v>
+        <v>6431</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>628884</v>
+        <v>629168</v>
       </c>
       <c r="R45" t="n">
-        <v>6631205</v>
+        <v>6630544</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6320,7 +6326,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>1 dm2 på barken på asplåga, omkr. 183 cm.</t>
+          <t>På levnade asp, omkr. 207 cm.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6334,7 +6340,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Medelåldrig blandskog med överståndare.</t>
+          <t>Äldre blandskog.</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -6349,7 +6355,7 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark på stammen av asplåga, omkr. 183 cm. # Populus tremula</t>
+          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6630,10 +6636,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124286769</v>
+        <v>124286768</v>
       </c>
       <c r="B48" t="n">
-        <v>6672</v>
+        <v>79926</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6642,25 +6648,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100763</v>
+        <v>6463</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cinnoberbagge</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cucujus cinnaberinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6668,19 +6674,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6729,7 +6725,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>1 larv under barken på asplåga, omkr. 183 cm.</t>
+          <t>1 dm2 på barken på asplåga, omkr. 183 cm.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6758,7 +6754,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Bark på stammen av asplåga, omkr. 183 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6776,10 +6772,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124286781</v>
+        <v>124286780</v>
       </c>
       <c r="B49" t="n">
-        <v>5361</v>
+        <v>6672</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6788,31 +6784,45 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>101728</v>
+        <v>100763</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Cinnoberbagge</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Cucujus cinnaberinus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6861,7 +6871,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Färska puppkamrar (ingångshål tilltäppta med ljusa, grova vedspånor) i asphögstubbe, omkr. 137 cm.</t>
+          <t>1 larv under barken på asphögstubbe, omkr. 137 cm.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6908,10 +6918,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124286780</v>
+        <v>124286776</v>
       </c>
       <c r="B50" t="n">
-        <v>6672</v>
+        <v>95551</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6920,45 +6930,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100763</v>
+        <v>210</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cinnoberbagge</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cucujus cinnaberinus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6967,10 +6967,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628826</v>
+        <v>629163</v>
       </c>
       <c r="R50" t="n">
-        <v>6630334</v>
+        <v>6630553</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>1 larv under barken på asphögstubbe, omkr. 137 cm.</t>
+          <t>3 kapslar på starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7021,22 +7021,22 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Äldre blandskog där granarna har dött.</t>
+          <t>Äldre blandskog.</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm. # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>

--- a/artfynd/A 51297-2024 artfynd.xlsx
+++ b/artfynd/A 51297-2024 artfynd.xlsx
@@ -5841,10 +5841,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124286769</v>
+        <v>124286781</v>
       </c>
       <c r="B42" t="n">
-        <v>6672</v>
+        <v>5361</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5853,45 +5853,31 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100763</v>
+        <v>101728</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cinnoberbagge</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cucujus cinnaberinus</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+          <t>(Pallas, 1773)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5900,10 +5886,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628884</v>
+        <v>628826</v>
       </c>
       <c r="R42" t="n">
-        <v>6631205</v>
+        <v>6630334</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5940,7 +5926,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>1 larv under barken på asplåga, omkr. 183 cm.</t>
+          <t>Färska puppkamrar (ingångshål tilltäppta med ljusa, grova vedspånor) i asphögstubbe, omkr. 137 cm.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5954,7 +5940,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Medelåldrig blandskog med överståndare.</t>
+          <t>Äldre blandskog där granarna har dött.</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -5987,10 +5973,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124286781</v>
+        <v>124286768</v>
       </c>
       <c r="B43" t="n">
-        <v>5361</v>
+        <v>79926</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5999,31 +5985,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>101728</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -6032,10 +6022,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628826</v>
+        <v>628884</v>
       </c>
       <c r="R43" t="n">
-        <v>6630334</v>
+        <v>6631205</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6072,7 +6062,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färska puppkamrar (ingångshål tilltäppta med ljusa, grova vedspånor) i asphögstubbe, omkr. 137 cm.</t>
+          <t>1 dm2 på barken på asplåga, omkr. 183 cm.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6086,7 +6076,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Äldre blandskog där granarna har dött.</t>
+          <t>Medelåldrig blandskog med överståndare.</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6101,7 +6091,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Bark på stammen av asplåga, omkr. 183 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6119,10 +6109,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124286778</v>
+        <v>124286775</v>
       </c>
       <c r="B44" t="n">
-        <v>80104</v>
+        <v>79920</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6131,38 +6121,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228430</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rostorangelav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Blastenia ferruginea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Huds.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>629196</v>
+        <v>629168</v>
       </c>
       <c r="R44" t="n">
-        <v>6630570</v>
+        <v>6630544</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6199,7 +6198,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm.</t>
+          <t>5 cm2 på levnade asp, omkr. 207 cm.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6213,7 +6212,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Äldre barr-/blandskog med mycket död gran.</t>
+          <t>Äldre blandskog.</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -6228,7 +6227,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm. # Populus tremula</t>
+          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6246,10 +6245,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124286773</v>
+        <v>124286769</v>
       </c>
       <c r="B45" t="n">
-        <v>79190</v>
+        <v>6672</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6258,38 +6257,57 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6431</v>
+        <v>100763</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Cinnoberbagge</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Cucujus cinnaberinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>629168</v>
+        <v>628884</v>
       </c>
       <c r="R45" t="n">
-        <v>6630544</v>
+        <v>6631205</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6326,7 +6344,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På levnade asp, omkr. 207 cm.</t>
+          <t>1 larv under barken på asplåga, omkr. 183 cm.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6340,7 +6358,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Äldre blandskog.</t>
+          <t>Medelåldrig blandskog med överståndare.</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -6355,7 +6373,7 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6373,7 +6391,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124286770</v>
+        <v>124286778</v>
       </c>
       <c r="B46" t="n">
         <v>80104</v>
@@ -6413,10 +6431,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>628939</v>
+        <v>629196</v>
       </c>
       <c r="R46" t="n">
-        <v>6631046</v>
+        <v>6630570</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6453,7 +6471,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm.</t>
+          <t>På bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6467,7 +6485,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Medelåldrig blandskog med överståndare.</t>
+          <t>Äldre barr-/blandskog med mycket död gran.</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -6482,7 +6500,7 @@
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm. # Populus tremula</t>
+          <t>Bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6500,10 +6518,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124286775</v>
+        <v>124286776</v>
       </c>
       <c r="B47" t="n">
-        <v>79920</v>
+        <v>95551</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6516,31 +6534,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>210</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6549,10 +6567,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>629168</v>
+        <v>629163</v>
       </c>
       <c r="R47" t="n">
-        <v>6630544</v>
+        <v>6630553</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6589,7 +6607,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>5 cm2 på levnade asp, omkr. 207 cm.</t>
+          <t>3 kapslar på starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6608,17 +6626,17 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
+          <t>Starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm. # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6636,10 +6654,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124286768</v>
+        <v>124286770</v>
       </c>
       <c r="B48" t="n">
-        <v>79926</v>
+        <v>80104</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6648,47 +6666,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6463</v>
+        <v>228430</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rostorangelav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Blastenia ferruginea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Huds.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628884</v>
+        <v>628939</v>
       </c>
       <c r="R48" t="n">
-        <v>6631205</v>
+        <v>6631046</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6725,7 +6734,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>1 dm2 på barken på asplåga, omkr. 183 cm.</t>
+          <t>På bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6754,7 +6763,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark på stammen av asplåga, omkr. 183 cm. # Populus tremula</t>
+          <t>Bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6772,10 +6781,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124286780</v>
+        <v>124286773</v>
       </c>
       <c r="B49" t="n">
-        <v>6672</v>
+        <v>79190</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6784,57 +6793,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100763</v>
+        <v>6431</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cinnoberbagge</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cucujus cinnaberinus</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628826</v>
+        <v>629168</v>
       </c>
       <c r="R49" t="n">
-        <v>6630334</v>
+        <v>6630544</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6871,7 +6861,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>1 larv under barken på asphögstubbe, omkr. 137 cm.</t>
+          <t>På levnade asp, omkr. 207 cm.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6885,7 +6875,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Äldre blandskog där granarna har dött.</t>
+          <t>Äldre blandskog.</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -6900,7 +6890,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6918,10 +6908,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124286776</v>
+        <v>124286780</v>
       </c>
       <c r="B50" t="n">
-        <v>95551</v>
+        <v>6672</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6930,35 +6920,45 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>210</v>
+        <v>100763</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Cinnoberbagge</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Cucujus cinnaberinus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6967,10 +6967,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>629163</v>
+        <v>628826</v>
       </c>
       <c r="R50" t="n">
-        <v>6630553</v>
+        <v>6630334</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>3 kapslar på starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm.</t>
+          <t>1 larv under barken på asphögstubbe, omkr. 137 cm.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7021,22 +7021,22 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Äldre blandskog.</t>
+          <t>Äldre blandskog där granarna har dött.</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm. # Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>

--- a/artfynd/A 51297-2024 artfynd.xlsx
+++ b/artfynd/A 51297-2024 artfynd.xlsx
@@ -5841,10 +5841,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124286781</v>
+        <v>124286776</v>
       </c>
       <c r="B42" t="n">
-        <v>5361</v>
+        <v>95551</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5853,31 +5853,35 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>101728</v>
+        <v>210</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5886,10 +5890,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628826</v>
+        <v>629163</v>
       </c>
       <c r="R42" t="n">
-        <v>6630334</v>
+        <v>6630553</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5926,7 +5930,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färska puppkamrar (ingångshål tilltäppta med ljusa, grova vedspånor) i asphögstubbe, omkr. 137 cm.</t>
+          <t>3 kapslar på starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5940,22 +5944,22 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Äldre blandskog där granarna har dött.</t>
+          <t>Äldre blandskog.</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm. # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5973,10 +5977,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124286768</v>
+        <v>124286775</v>
       </c>
       <c r="B43" t="n">
-        <v>79926</v>
+        <v>79920</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5989,31 +5993,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -6022,10 +6026,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628884</v>
+        <v>629168</v>
       </c>
       <c r="R43" t="n">
-        <v>6631205</v>
+        <v>6630544</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6062,7 +6066,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>1 dm2 på barken på asplåga, omkr. 183 cm.</t>
+          <t>5 cm2 på levnade asp, omkr. 207 cm.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6076,7 +6080,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Medelåldrig blandskog med överståndare.</t>
+          <t>Äldre blandskog.</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6091,7 +6095,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark på stammen av asplåga, omkr. 183 cm. # Populus tremula</t>
+          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6109,10 +6113,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124286775</v>
+        <v>124286768</v>
       </c>
       <c r="B44" t="n">
-        <v>79920</v>
+        <v>79926</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6125,31 +6129,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6158,10 +6162,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>629168</v>
+        <v>628884</v>
       </c>
       <c r="R44" t="n">
-        <v>6630544</v>
+        <v>6631205</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6198,7 +6202,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>5 cm2 på levnade asp, omkr. 207 cm.</t>
+          <t>1 dm2 på barken på asplåga, omkr. 183 cm.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6212,7 +6216,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Äldre blandskog.</t>
+          <t>Medelåldrig blandskog med överståndare.</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -6227,7 +6231,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
+          <t>Bark på stammen av asplåga, omkr. 183 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6245,10 +6249,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124286769</v>
+        <v>124286773</v>
       </c>
       <c r="B45" t="n">
-        <v>6672</v>
+        <v>79190</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6257,57 +6261,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100763</v>
+        <v>6431</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cinnoberbagge</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cucujus cinnaberinus</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>628884</v>
+        <v>629168</v>
       </c>
       <c r="R45" t="n">
-        <v>6631205</v>
+        <v>6630544</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6344,7 +6329,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>1 larv under barken på asplåga, omkr. 183 cm.</t>
+          <t>På levnade asp, omkr. 207 cm.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6358,7 +6343,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Medelåldrig blandskog med överståndare.</t>
+          <t>Äldre blandskog.</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -6373,7 +6358,7 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6391,10 +6376,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124286778</v>
+        <v>124286769</v>
       </c>
       <c r="B46" t="n">
-        <v>80104</v>
+        <v>6672</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6403,38 +6388,57 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228430</v>
+        <v>100763</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rostorangelav</t>
+          <t>Cinnoberbagge</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Blastenia ferruginea</t>
+          <t>Cucujus cinnaberinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Huds.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>629196</v>
+        <v>628884</v>
       </c>
       <c r="R46" t="n">
-        <v>6630570</v>
+        <v>6631205</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6471,7 +6475,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm.</t>
+          <t>1 larv under barken på asplåga, omkr. 183 cm.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6485,7 +6489,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Äldre barr-/blandskog med mycket död gran.</t>
+          <t>Medelåldrig blandskog med överståndare.</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -6500,7 +6504,7 @@
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm. # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6518,10 +6522,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124286776</v>
+        <v>124286770</v>
       </c>
       <c r="B47" t="n">
-        <v>95551</v>
+        <v>80104</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6530,47 +6534,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>210</v>
+        <v>228430</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Rostorangelav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Blastenia ferruginea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Huds.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>629163</v>
+        <v>628939</v>
       </c>
       <c r="R47" t="n">
-        <v>6630553</v>
+        <v>6631046</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6607,7 +6602,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>3 kapslar på starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm.</t>
+          <t>På bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6621,22 +6616,22 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Äldre blandskog.</t>
+          <t>Medelåldrig blandskog med överståndare.</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm. # Picea abies</t>
+          <t>Bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6654,10 +6649,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124286770</v>
+        <v>124286780</v>
       </c>
       <c r="B48" t="n">
-        <v>80104</v>
+        <v>6672</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6666,38 +6661,57 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228430</v>
+        <v>100763</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rostorangelav</t>
+          <t>Cinnoberbagge</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Blastenia ferruginea</t>
+          <t>Cucujus cinnaberinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Huds.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628939</v>
+        <v>628826</v>
       </c>
       <c r="R48" t="n">
-        <v>6631046</v>
+        <v>6630334</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6734,7 +6748,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm.</t>
+          <t>1 larv under barken på asphögstubbe, omkr. 137 cm.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6748,7 +6762,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Medelåldrig blandskog med överståndare.</t>
+          <t>Äldre blandskog där granarna har dött.</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -6763,7 +6777,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm. # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6781,10 +6795,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124286773</v>
+        <v>124286781</v>
       </c>
       <c r="B49" t="n">
-        <v>79190</v>
+        <v>5361</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6793,38 +6807,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6431</v>
+        <v>101728</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>629168</v>
+        <v>628826</v>
       </c>
       <c r="R49" t="n">
-        <v>6630544</v>
+        <v>6630334</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6861,7 +6880,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På levnade asp, omkr. 207 cm.</t>
+          <t>Färska puppkamrar (ingångshål tilltäppta med ljusa, grova vedspånor) i asphögstubbe, omkr. 137 cm.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6875,7 +6894,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Äldre blandskog.</t>
+          <t>Äldre blandskog där granarna har dött.</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -6890,7 +6909,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6908,10 +6927,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124286780</v>
+        <v>124286778</v>
       </c>
       <c r="B50" t="n">
-        <v>6672</v>
+        <v>80104</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6920,57 +6939,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100763</v>
+        <v>228430</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cinnoberbagge</t>
+          <t>Rostorangelav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cucujus cinnaberinus</t>
+          <t>Blastenia ferruginea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Huds.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628826</v>
+        <v>629196</v>
       </c>
       <c r="R50" t="n">
-        <v>6630334</v>
+        <v>6630570</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>1 larv under barken på asphögstubbe, omkr. 137 cm.</t>
+          <t>På bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Äldre blandskog där granarna har dött.</t>
+          <t>Äldre barr-/blandskog med mycket död gran.</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>

--- a/artfynd/A 51297-2024 artfynd.xlsx
+++ b/artfynd/A 51297-2024 artfynd.xlsx
@@ -7057,7 +7057,7 @@
         <v>126768713</v>
       </c>
       <c r="B51" t="n">
-        <v>8458</v>
+        <v>8461</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 51297-2024 artfynd.xlsx
+++ b/artfynd/A 51297-2024 artfynd.xlsx
@@ -7057,7 +7057,7 @@
         <v>126768713</v>
       </c>
       <c r="B51" t="n">
-        <v>8461</v>
+        <v>8458</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 51297-2024 artfynd.xlsx
+++ b/artfynd/A 51297-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74811587</v>
+        <v>124286776</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>627610.5681573031</v>
+        <v>629163</v>
       </c>
       <c r="R2" t="n">
-        <v>6630794.579482902</v>
+        <v>6630553</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,27 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1997-08-31</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1997-08-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>5 dm2 på stammen av levande sälg, omkr. 90 cm.</t>
+          <t>3 kapslar på starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,14 +771,24 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Sälg</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Äldre blandskog.</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stammen av levande sälg. # Sälg</t>
+          <t>Starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm. # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,15 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74811572</v>
+        <v>74811591</v>
       </c>
       <c r="B3" t="n">
-        <v>78614</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80703</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229504</v>
+        <v>226</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Skuggorangelav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Caloplaca lucifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -851,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>627841.4503164027</v>
+        <v>627792</v>
       </c>
       <c r="R3" t="n">
-        <v>6630697.740988991</v>
+        <v>6629867</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -884,24 +874,14 @@
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På stammen av levande asp, omkr. 164 cm.</t>
+          <t>På stammen av levande ek, omkr. 263 cm.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,12 +895,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>Skogsek</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stammen av levande asp. # Asp</t>
+          <t>Stammen av levande ek. # Skogsek</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -938,37 +918,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74811575</v>
+        <v>126768714</v>
       </c>
       <c r="B4" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80703</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>226</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skuggorangelav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Caloplaca lucifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -978,13 +953,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>627841.4503164027</v>
+        <v>627759</v>
       </c>
       <c r="R4" t="n">
-        <v>6630697.740988991</v>
+        <v>6629895</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,27 +983,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1997-08-31</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1997-08-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På stammen av levande asp.</t>
+          <t>På levande, ihålig ek, omkr. 275 cm.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,16 +1005,27 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Asp</t>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Medelåldrig blandskog med några överståndare.</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stammen av levande asp. # Asp</t>
-        </is>
-      </c>
+          <t>Stammen av levande, ihålig ek, omkr. 275 cm. # Quercus robur</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1065,50 +1041,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74811582</v>
+        <v>74811577</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80465</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1083</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Västlig njurlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma laevigatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627841.4503164027</v>
+        <v>628251</v>
       </c>
       <c r="R5" t="n">
-        <v>6630697.740988991</v>
+        <v>6630703</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1138,24 +1118,14 @@
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På stammen av levande asp.</t>
+          <t>4 dm2 på stammen av levande sälg, omkr. 88 cm.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,17 +1134,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stammen av levande asp. # Asp</t>
+          <t>Stammen av levande sälg. # Sälg</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1192,50 +1163,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>74811590</v>
+        <v>74811578</v>
       </c>
       <c r="B6" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80465</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>1083</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Västlig njurlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma laevigatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627841.4503164027</v>
+        <v>628043</v>
       </c>
       <c r="R6" t="n">
-        <v>6630697.740988991</v>
+        <v>6630610</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1265,24 +1240,14 @@
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På stammen av levande asp, omkr. 164 cm.</t>
+          <t>2 dm2 på stammen av levande asp, omkr. 109 cm.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1291,6 +1256,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1319,37 +1285,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>74811581</v>
+        <v>74811579</v>
       </c>
       <c r="B7" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80465</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>1083</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Västlig njurlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma laevigatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1368,10 +1329,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627610.5681573031</v>
+        <v>627611</v>
       </c>
       <c r="R7" t="n">
-        <v>6630794.579482902</v>
+        <v>6630795</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1401,21 +1362,11 @@
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>1 dm2 på stammen av levande sälg, omkr. 90 cm.</t>
@@ -1427,6 +1378,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1455,15 +1407,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>74811579</v>
+        <v>74811580</v>
       </c>
       <c r="B8" t="n">
-        <v>78600</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80465</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,10 +1451,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>627610.5681573031</v>
+        <v>628252</v>
       </c>
       <c r="R8" t="n">
-        <v>6630794.579482902</v>
+        <v>6630683</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1537,24 +1484,14 @@
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 dm2 på stammen av levande sälg, omkr. 90 cm.</t>
+          <t>1 dm2 på bark på stammen av död, stående sälg, omkr. 37 cm.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1574,7 +1511,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stammen av levande sälg. # Sälg</t>
+          <t>Bark på stammen av död, stående sälg. # Sälg</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1592,15 +1529,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>75082690</v>
+        <v>75082670</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1627,7 +1559,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1641,13 +1573,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>627338.7928709007</v>
+        <v>628685</v>
       </c>
       <c r="R9" t="n">
-        <v>6630951.475957199</v>
+        <v>6630448</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1671,27 +1603,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1997-08-31</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-10-24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1997-08-31</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-10-24</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 dm2 på granlåga (rotvälta), omkr. 45 cm.</t>
+          <t>2 dm2 på granlåga, omkr. 95 cm.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1710,7 +1632,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Granlåga, (rotvälta). # Gran</t>
+          <t>Granlåga. # Gran</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1728,47 +1650,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>75085742</v>
+        <v>75082690</v>
       </c>
       <c r="B10" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1777,13 +1694,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>627630.7264260456</v>
+        <v>627339</v>
       </c>
       <c r="R10" t="n">
-        <v>6630795.271367501</v>
+        <v>6630951</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1810,24 +1727,14 @@
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>8 ex. på stammen av levande asp, omkr. 157 cm.</t>
+          <t>1 dm2 på granlåga (rotvälta), omkr. 45 cm.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1841,12 +1748,12 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stammen av levande asp. # Asp</t>
+          <t>Granlåga, (rotvälta). # Gran</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1864,42 +1771,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>74631900</v>
+        <v>75085742</v>
       </c>
       <c r="B11" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>1205</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1908,13 +1815,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>627641.1792713043</v>
+        <v>627631</v>
       </c>
       <c r="R11" t="n">
-        <v>6630755.334655233</v>
+        <v>6630795</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1938,27 +1845,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>1997-10-09</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-08-31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1997-10-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-08-31</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>3-4 ex.</t>
+          <t>8 ex. på stammen av levande asp, omkr. 157 cm.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1969,6 +1866,16 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stammen av levande asp. # Asp</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1985,62 +1892,59 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20661272</v>
+        <v>83042174</v>
       </c>
       <c r="B12" t="n">
-        <v>56410</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>1445</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Degermossen, Skogstibble skjutfält, Upl</t>
+          <t>Degermossen, S om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>628204.542226515</v>
+        <v>628189</v>
       </c>
       <c r="R12" t="n">
-        <v>6631127.793557435</v>
+        <v>6630465</v>
       </c>
       <c r="S12" t="n">
-        <v>419</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2064,22 +1968,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2005-02-06</t>
+          <t>2020-03-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2005-02-06</t>
+          <t>2020-03-21</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>17 bombmurklor strax intill nyligen vindfälld gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2088,76 +1997,72 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Martin Tjernberg</t>
+          <t>Gabriel Tjernberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Martin Tjernberg</t>
+          <t>Gabriel Tjernberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>22365469</v>
+        <v>74811571</v>
       </c>
       <c r="B13" t="n">
-        <v>57009</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102124</v>
+        <v>1467</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vinterhämpling</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Linaria flavirostris</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Degermossen, Skogstibble skjutfält, Upl</t>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628204.542226515</v>
+        <v>627792</v>
       </c>
       <c r="R13" t="n">
-        <v>6631127.793557435</v>
+        <v>6629867</v>
       </c>
       <c r="S13" t="n">
-        <v>419</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2181,27 +2086,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>1988-04-18</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-08-31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1988-04-18</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-08-31</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>norr om</t>
+          <t>På stammen av levande ek, omkr. 263 cm.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2212,31 +2107,36 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stammen av levande ek. # Skogsek</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Martin Tjernberg</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Martin Tjernberg</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>22368531</v>
+        <v>124286782</v>
       </c>
       <c r="B14" t="n">
-        <v>56285</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2244,46 +2144,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100001</v>
+        <v>1467</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Degermossen, Skogstibble skjutfält, Upl</t>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628204.542226515</v>
+        <v>627755</v>
       </c>
       <c r="R14" t="n">
-        <v>6631127.793557435</v>
+        <v>6629900</v>
       </c>
       <c r="S14" t="n">
-        <v>419</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2307,27 +2198,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>1988-04-18</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1988-04-18</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>strax norr om, kretsar på låg höjd</t>
+          <t>På levande ek, omkr. 210 cm.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2338,31 +2219,46 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Medelåldrig blandskog med några överståndare.</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stammen av levande ek, omkr. 210 cm. # Quercus robur</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Martin Tjernberg</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Martin Tjernberg</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>23241383</v>
+        <v>124286784</v>
       </c>
       <c r="B15" t="n">
-        <v>56805</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2370,46 +2266,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103001</v>
+        <v>1467</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Degermossen, Skogstibble skjutfält, Upl</t>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628204.542226515</v>
+        <v>627759</v>
       </c>
       <c r="R15" t="n">
-        <v>6631127.793557435</v>
+        <v>6629895</v>
       </c>
       <c r="S15" t="n">
-        <v>419</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2433,22 +2320,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2006-04-14</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2006-04-14</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt på levande, ihålig ek, omkr. 275 cm.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2459,31 +2341,46 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Medelåldrig blandskog med några överståndare.</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stammen av levande, ihålig ek, omkr. 275 cm. # Quercus robur</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Stefan Larsson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Stefan Larsson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>25238181</v>
+        <v>75073801</v>
       </c>
       <c r="B16" t="n">
-        <v>56394</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92732</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2491,21 +2388,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>2014</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2513,24 +2410,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Degermossen, Skogstibble skjutfält, Upl</t>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628204.542226515</v>
+        <v>628241</v>
       </c>
       <c r="R16" t="n">
-        <v>6631127.793557435</v>
+        <v>6630742</v>
       </c>
       <c r="S16" t="n">
-        <v>419</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2554,27 +2451,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>1991-03-16</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>06:00</t>
+          <t>1997-08-31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1991-03-16</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>06:10</t>
+          <t>1997-08-31</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>trummar ett 10-tal ggr från V sidan Degermossen</t>
+          <t>1 ex. på murken asplåga, omkr. ca. 110 cm.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2585,78 +2472,74 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Murken asplåga. # Asp</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Martin Tjernberg</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Martin Tjernberg</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>37859799</v>
+        <v>74962989</v>
       </c>
       <c r="B17" t="n">
-        <v>56539</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>2667</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Degermossen, Skogstibble skjutfält, Upl</t>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628204.542226515</v>
+        <v>628043</v>
       </c>
       <c r="R17" t="n">
-        <v>6631127.793557435</v>
+        <v>6630610</v>
       </c>
       <c r="S17" t="n">
-        <v>419</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2680,22 +2563,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2011-01-15</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-08-31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2011-01-15</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-08-31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På stenblock.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2706,64 +2584,69 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stenblock.</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Yngve Hareland</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Yngve Hareland, Lotta Hedkvist</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>65889562</v>
+        <v>75073990</v>
       </c>
       <c r="B18" t="n">
-        <v>102159</v>
+        <v>92632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221223</v>
+        <v>3298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skogs-Tibble skjutfält, 200 m NO om Björnkällan, Upl</t>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628502</v>
+        <v>628147</v>
       </c>
       <c r="R18" t="n">
-        <v>6630221</v>
+        <v>6630261</v>
       </c>
       <c r="S18" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2787,17 +2670,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>1997-08-31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2003-12-31</t>
+          <t>1997-08-31</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Upplandsfloran - detaljuppgifter. Observatör Per Kornhall</t>
+          <t>På död, stående gran, omkr. 115 cm.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2808,57 +2691,58 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Död, stående gran. # Gran</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Via Mora Aronsson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Upplands Flora 2010</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>74741293</v>
+        <v>75073745</v>
       </c>
       <c r="B19" t="n">
-        <v>99382</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221223</v>
+        <v>4660</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2868,10 +2752,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>628744.4966033162</v>
+        <v>628744</v>
       </c>
       <c r="R19" t="n">
-        <v>6630468.469887933</v>
+        <v>6630468</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2901,24 +2785,14 @@
           <t>1997-09-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>1997-09-01</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Några plantor i ett aspbestånd.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2929,6 +2803,16 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2945,15 +2829,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>74811576</v>
+        <v>75073528</v>
       </c>
       <c r="B20" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2961,21 +2840,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>5321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2985,13 +2864,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>628251.6801034858</v>
+        <v>628043</v>
       </c>
       <c r="R20" t="n">
-        <v>6630682.652419033</v>
+        <v>6630610</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3018,24 +2897,14 @@
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På bark på stammen av död, stående sälg, omkr. 37 cm.</t>
+          <t>På asplåga, omkr. 102 cm.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3049,12 +2918,12 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark på stammen av död, stående sälg. # Sälg</t>
+          <t>Asplåga. # Asp</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3072,62 +2941,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>74811577</v>
+        <v>124286773</v>
       </c>
       <c r="B21" t="n">
-        <v>78600</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79707</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1083</v>
+        <v>6431</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Västlig njurlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma laevigatum</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628251.4899599819</v>
+        <v>629168</v>
       </c>
       <c r="R21" t="n">
-        <v>6630702.79433402</v>
+        <v>6630544</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3151,27 +3006,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>1997-08-31</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1997-08-31</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>4 dm2 på stammen av levande sälg, omkr. 88 cm.</t>
+          <t>På levnade asp, omkr. 207 cm.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3180,18 +3025,27 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>Sälg</t>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Äldre blandskog.</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stammen av levande sälg. # Sälg</t>
+          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3212,12 +3066,7 @@
         <v>74811589</v>
       </c>
       <c r="B22" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3249,10 +3098,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628147.1151618415</v>
+        <v>628147</v>
       </c>
       <c r="R22" t="n">
-        <v>6630261.446366942</v>
+        <v>6630261</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3282,19 +3131,9 @@
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>1997-08-31</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3336,59 +3175,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>74811588</v>
+        <v>74811590</v>
       </c>
       <c r="B23" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628251.6801034858</v>
+        <v>627841</v>
       </c>
       <c r="R23" t="n">
-        <v>6630682.652419033</v>
+        <v>6630698</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3418,24 +3243,14 @@
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2 dm2 på bark på stammen av död, stående sälg, omkr. 37 cm.</t>
+          <t>På stammen av levande asp, omkr. 164 cm.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3449,12 +3264,12 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark på stammen av död, stående sälg. # Sälg</t>
+          <t>Stammen av levande asp. # Asp</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3472,15 +3287,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>74811586</v>
+        <v>74811582</v>
       </c>
       <c r="B24" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3505,26 +3315,17 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>628251.4899599819</v>
+        <v>627841</v>
       </c>
       <c r="R24" t="n">
-        <v>6630702.79433402</v>
+        <v>6630698</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3554,24 +3355,14 @@
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ca. 15 dm2 på stammen av levande sälg, omkr. 88 cm.</t>
+          <t>På stammen av levande asp.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3585,12 +3376,12 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stammen av levande sälg. # Sälg</t>
+          <t>Stammen av levande asp. # Asp</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3608,15 +3399,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>74811584</v>
+        <v>74811583</v>
       </c>
       <c r="B25" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3648,10 +3434,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628042.7674774055</v>
+        <v>628043</v>
       </c>
       <c r="R25" t="n">
-        <v>6630609.969595331</v>
+        <v>6630610</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3681,24 +3467,14 @@
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På stammar av sex levande aspar.</t>
+          <t>På stammar av två levande lindar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3712,12 +3488,12 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>Skogslind</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stammar av levande aspar. # Asp</t>
+          <t>Stammar av levande lindar. # Skogslind</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3738,12 +3514,7 @@
         <v>74811585</v>
       </c>
       <c r="B26" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3775,10 +3546,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628251.1270169024</v>
+        <v>628251</v>
       </c>
       <c r="R26" t="n">
-        <v>6630742.574731453</v>
+        <v>6630743</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3808,19 +3579,9 @@
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>1997-08-31</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3862,42 +3623,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>74811578</v>
+        <v>74811586</v>
       </c>
       <c r="B27" t="n">
-        <v>78600</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1083</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Västlig njurlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma laevigatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3911,10 +3667,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628042.7674774055</v>
+        <v>628251</v>
       </c>
       <c r="R27" t="n">
-        <v>6630609.969595331</v>
+        <v>6630703</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3944,24 +3700,14 @@
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2 dm2 på stammen av levande asp, omkr. 109 cm.</t>
+          <t>Ca. 15 dm2 på stammen av levande sälg, omkr. 88 cm.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3970,18 +3716,17 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stammen av levande asp. # Asp</t>
+          <t>Stammen av levande sälg. # Sälg</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3999,42 +3744,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>74811580</v>
+        <v>74811587</v>
       </c>
       <c r="B28" t="n">
-        <v>78600</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1083</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Västlig njurlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma laevigatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4048,10 +3788,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628251.6801034858</v>
+        <v>627611</v>
       </c>
       <c r="R28" t="n">
-        <v>6630682.652419033</v>
+        <v>6630795</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -4081,24 +3821,14 @@
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>1 dm2 på bark på stammen av död, stående sälg, omkr. 37 cm.</t>
+          <t>5 dm2 på stammen av levande sälg, omkr. 90 cm.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4107,7 +3837,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4118,7 +3847,7 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark på stammen av död, stående sälg. # Sälg</t>
+          <t>Stammen av levande sälg. # Sälg</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4136,50 +3865,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>74962989</v>
+        <v>74811588</v>
       </c>
       <c r="B29" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2667</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628042.7674774055</v>
+        <v>628252</v>
       </c>
       <c r="R29" t="n">
-        <v>6630609.969595331</v>
+        <v>6630683</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4209,24 +3942,14 @@
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På stenblock.</t>
+          <t>2 dm2 på bark på stammen av död, stående sälg, omkr. 37 cm.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4238,9 +3961,14 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stenblock.</t>
+          <t>Bark på stammen av död, stående sälg. # Sälg</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4258,37 +3986,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>75073801</v>
+        <v>74811581</v>
       </c>
       <c r="B30" t="n">
-        <v>90174</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2014</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Pers.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4298,7 +4021,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4307,13 +4030,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>628241.0477203613</v>
+        <v>627611</v>
       </c>
       <c r="R30" t="n">
-        <v>6630742.227095205</v>
+        <v>6630795</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4340,24 +4063,14 @@
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>1 ex. på murken asplåga, omkr. ca. 110 cm.</t>
+          <t>1 dm2 på stammen av levande sälg, omkr. 90 cm.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4371,12 +4084,12 @@
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Murken asplåga. # Asp</t>
+          <t>Stammen av levande sälg. # Sälg</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4394,15 +4107,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>75073745</v>
+        <v>124286775</v>
       </c>
       <c r="B31" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4410,37 +4118,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4660</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>628744.4966033162</v>
+        <v>629168</v>
       </c>
       <c r="R31" t="n">
-        <v>6630468.469887933</v>
+        <v>6630544</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4464,27 +4181,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>1997-09-01</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>1997-09-01</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>5 cm2 på levnade asp, omkr. 207 cm.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4496,14 +4203,24 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>Asp</t>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Äldre blandskog.</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Asp</t>
+          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4521,15 +4238,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>75073528</v>
+        <v>74811575</v>
       </c>
       <c r="B32" t="n">
-        <v>89794</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4537,21 +4249,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5321</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4561,13 +4273,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628042.7674774055</v>
+        <v>627841</v>
       </c>
       <c r="R32" t="n">
-        <v>6630609.969595331</v>
+        <v>6630698</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4594,24 +4306,14 @@
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>1997-08-31</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På asplåga, omkr. 102 cm.</t>
+          <t>På stammen av levande asp.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4630,7 +4332,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Asplåga. # Asp</t>
+          <t>Stammen av levande asp. # Asp</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4648,59 +4350,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>75082670</v>
+        <v>74811576</v>
       </c>
       <c r="B33" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628684.6604712533</v>
+        <v>628252</v>
       </c>
       <c r="R33" t="n">
-        <v>6630447.760113939</v>
+        <v>6630683</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4727,27 +4415,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>1997-10-24</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-08-31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>1997-10-24</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-08-31</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>2 dm2 på granlåga, omkr. 95 cm.</t>
+          <t>På bark på stammen av död, stående sälg, omkr. 37 cm.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4761,12 +4439,12 @@
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Granlåga. # Gran</t>
+          <t>Bark på stammen av död, stående sälg. # Sälg</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4784,15 +4462,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>75073990</v>
+        <v>124286768</v>
       </c>
       <c r="B34" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4800,37 +4473,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3298</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628147.1151618415</v>
+        <v>628884</v>
       </c>
       <c r="R34" t="n">
-        <v>6630261.446366942</v>
+        <v>6631205</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4854,27 +4536,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>1997-08-31</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>1997-08-31</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På död, stående gran, omkr. 115 cm.</t>
+          <t>1 dm2 på barken på asplåga, omkr. 183 cm.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4886,14 +4558,24 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>Gran</t>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Medelåldrig blandskog med överståndare.</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Död, stående gran. # Gran</t>
+          <t>Bark på stammen av asplåga, omkr. 183 cm. # Populus tremula</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4911,15 +4593,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>75200960</v>
+        <v>22368531</v>
       </c>
       <c r="B35" t="n">
-        <v>5295</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4927,42 +4604,46 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>101728</v>
+        <v>100001</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+          <t>Degermossen, Skogstibble skjutfält, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>628153.2424592739</v>
+        <v>628205</v>
       </c>
       <c r="R35" t="n">
-        <v>6629761.38168182</v>
+        <v>6631128</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>419</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4986,7 +4667,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>1997-10-28</t>
+          <t>1988-04-18</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -4996,7 +4677,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>1997-10-28</t>
+          <t>1988-04-18</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -5006,7 +4687,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Puppkamrar i asplåga på ett gammalt hygge.</t>
+          <t>strax norr om, kretsar på låg höjd</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5017,90 +4698,73 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AL35" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Martin Tjernberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Martin Tjernberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>83042174</v>
+        <v>18140628</v>
       </c>
       <c r="B36" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1445</v>
+        <v>100038</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Degermossen, S om, Upl</t>
+          <t>Degermossen, Skogstibble skjutfält, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>628188.5469604991</v>
+        <v>628205</v>
       </c>
       <c r="R36" t="n">
-        <v>6630464.880152726</v>
+        <v>6631128</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>419</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5124,27 +4788,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2020-03-21</t>
+          <t>2002-04-02</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2020-03-21</t>
+          <t>2002-04-02</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>17 bombmurklor strax intill nyligen vindfälld gran</t>
+          <t>Ö delen</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5153,39 +4817,28 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg</t>
+          <t>Pekka Westin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg</t>
+          <t>Pekka Westin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>81991756</v>
+        <v>48456378</v>
       </c>
       <c r="B37" t="n">
-        <v>5295</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5193,46 +4846,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>101728</v>
+        <v>100048</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+          <t>Degermossen, Skogstibble skjutfält, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628992.6841214733</v>
+        <v>628205</v>
       </c>
       <c r="R37" t="n">
-        <v>6630994.385035542</v>
+        <v>6631128</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>419</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5256,27 +4909,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2020-01-02</t>
+          <t>2014-03-02</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2020-01-02</t>
+          <t>2014-03-02</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska puppkamrar (ingångshål tilltäppta med ljusa, grova vedspånor) i asplåga, omkr. 182 cm.</t>
+          <t>Porsmossen, norra delen, fuktig gammal lövskogssänka</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5285,66 +4938,45 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Blandskog med inslag av äldre asp.</t>
-        </is>
-      </c>
-      <c r="AL37" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Yngve Hareland</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Yngve Hareland</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>31403224</v>
+        <v>20661272</v>
       </c>
       <c r="B38" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5359,7 +4991,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5368,10 +5000,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>628204.542226515</v>
+        <v>628205</v>
       </c>
       <c r="R38" t="n">
-        <v>6631127.793557435</v>
+        <v>6631128</v>
       </c>
       <c r="S38" t="n">
         <v>419</v>
@@ -5398,7 +5030,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2009-01-09</t>
+          <t>2005-02-06</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
@@ -5408,17 +5040,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2009-01-09</t>
+          <t>2005-02-06</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Flög över vägen NO om Degermossen.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5433,74 +5060,71 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulrik Lötberg</t>
+          <t>Martin Tjernberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulrik Lötberg</t>
+          <t>Martin Tjernberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>83884583</v>
+        <v>19368304</v>
       </c>
       <c r="B39" t="n">
-        <v>56364</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100137</v>
+        <v>100065</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Slaguggla</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Strix uralensis</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Pallas, 1771</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Degermossen, Skogstibble skjutfält, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>628204.542226515</v>
+        <v>628205</v>
       </c>
       <c r="R39" t="n">
-        <v>6631127.793557435</v>
+        <v>6631128</v>
       </c>
       <c r="S39" t="n">
         <v>419</v>
@@ -5527,27 +5151,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2020-03-26</t>
+          <t>2004-05-01</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2020-03-26</t>
+          <t>2004-05-01</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Inte en av de två individerna jag tidigare rapporterade, denna sitter på helt annat ställe och ropar med det vanliga sånglätet.</t>
+          <t>ropar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5562,27 +5186,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Sundberg</t>
+          <t>Martin Tjernberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Sundberg, Daniel Ochterbeck</t>
+          <t>Martin Tjernberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>48456378</v>
+        <v>19235801</v>
       </c>
       <c r="B40" t="n">
-        <v>56401</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58067</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5590,16 +5209,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100048</v>
+        <v>100090</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5623,10 +5242,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>628204.542226515</v>
+        <v>628205</v>
       </c>
       <c r="R40" t="n">
-        <v>6631127.793557435</v>
+        <v>6631128</v>
       </c>
       <c r="S40" t="n">
         <v>419</v>
@@ -5653,27 +5272,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2014-03-02</t>
+          <t>2003-03-29</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2014-03-02</t>
+          <t>2003-03-29</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Porsmossen, norra delen, fuktig gammal lövskogssänka</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5688,49 +5302,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Yngve Hareland</t>
+          <t>Pekka Westin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Yngve Hareland</t>
+          <t>Pekka Westin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>23302483</v>
+        <v>124286779</v>
       </c>
       <c r="B41" t="n">
-        <v>56693</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58067</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100038</v>
+        <v>100090</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5738,29 +5347,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Degermossen, Skogstibble skjutfält, Upl</t>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>628205</v>
+        <v>628960</v>
       </c>
       <c r="R41" t="n">
-        <v>6631128</v>
+        <v>6630525</v>
       </c>
       <c r="S41" t="n">
-        <v>419</v>
+        <v>100</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5784,22 +5388,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2005-03-26</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2005-03-28</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5814,74 +5408,69 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Upplands Rapportkommitté</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jerker Mathson, Michael Åkerberg</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124286776</v>
+        <v>25238181</v>
       </c>
       <c r="B42" t="n">
-        <v>95551</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>210</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+          <t>Degermossen, Skogstibble skjutfält, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>629163</v>
+        <v>628205</v>
       </c>
       <c r="R42" t="n">
-        <v>6630553</v>
+        <v>6631128</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>419</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5905,17 +5494,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>1991-03-16</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>1991-03-16</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>06:10</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>3 kapslar på starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm.</t>
+          <t>trummar ett 10-tal ggr från V sidan Degermossen</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5926,51 +5525,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Äldre blandskog.</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Starkt murken, kapad, kvarlämnad granstock, omkr. ca. 120 cm. # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Martin Tjernberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Martin Tjernberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124286775</v>
+        <v>38065317</v>
       </c>
       <c r="B43" t="n">
-        <v>79920</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57945</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5978,46 +5552,46 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>100110</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>cm²</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+          <t>Degermossen, Skogstibble skjutfält, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>629168</v>
+        <v>628205</v>
       </c>
       <c r="R43" t="n">
-        <v>6630544</v>
+        <v>6631128</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>419</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6041,17 +5615,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>1999-04-02</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>1999-04-02</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>5 cm2 på levnade asp, omkr. 207 cm.</t>
+          <t>O om</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6062,51 +5646,26 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>Äldre blandskog.</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Åke Berg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Åke Berg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124286768</v>
+        <v>90672491</v>
       </c>
       <c r="B44" t="n">
-        <v>79926</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57945</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6114,21 +5673,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>100110</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -6136,24 +5695,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+          <t>Skogstibble skjutfält, Maskedal, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>628884</v>
+        <v>628715</v>
       </c>
       <c r="R44" t="n">
-        <v>6631205</v>
+        <v>6630998</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6177,17 +5731,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>1999-04-02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>1999-04-02</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>1 dm2 på barken på asplåga, omkr. 183 cm.</t>
+          <t>troligen hane</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6198,51 +5752,26 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Medelåldrig blandskog med överståndare.</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Bark på stammen av asplåga, omkr. 183 cm. # Populus tremula</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Anders Svenson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Anders Svenson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124286773</v>
+        <v>28367961</v>
       </c>
       <c r="B45" t="n">
-        <v>79190</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6250,37 +5779,51 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6431</v>
+        <v>100137</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Strix uralensis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>Pallas, 1771</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+          <t>Degermossen, Skogstibble skjutfält, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>629168</v>
+        <v>628205</v>
       </c>
       <c r="R45" t="n">
-        <v>6630544</v>
+        <v>6631128</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>419</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6304,17 +5847,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>1994-03-20</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>1994-03-20</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På levnade asp, omkr. 207 cm.</t>
+          <t>ropar revirlätet ett tiotal ggr från centrala delen av Degermossen 18:40-19:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6325,73 +5878,48 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Äldre blandskog.</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stammen av levnade asp, omkr. 207 cm. # Populus tremula</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Martin Tjernberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Martin Tjernberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124286769</v>
+        <v>76662286</v>
       </c>
       <c r="B46" t="n">
-        <v>6672</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100763</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cinnoberbagge</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cucujus cinnaberinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -6399,34 +5927,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+          <t>Degermossen, Skogstibble skjutfält, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>628884</v>
+        <v>628205</v>
       </c>
       <c r="R46" t="n">
-        <v>6631205</v>
+        <v>6631128</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>419</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6450,17 +5975,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2019-03-29</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2019-03-29</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>1 larv under barken på asplåga, omkr. 183 cm.</t>
+          <t>strax syd Degermossen</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6471,51 +6006,26 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Medelåldrig blandskog med överståndare.</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Yngve Hareland</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Yngve Hareland</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124286770</v>
+        <v>124286769</v>
       </c>
       <c r="B47" t="n">
-        <v>80104</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6675</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6523,34 +6033,53 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228430</v>
+        <v>100763</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rostorangelav</t>
+          <t>Cinnoberbagge</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Blastenia ferruginea</t>
+          <t>Cucujus cinnaberinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Huds.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628939</v>
+        <v>628884</v>
       </c>
       <c r="R47" t="n">
-        <v>6631046</v>
+        <v>6631205</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6587,7 +6116,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm.</t>
+          <t>1 larv under barken på asplåga, omkr. 183 cm.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6616,7 +6145,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm. # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6637,16 +6166,11 @@
         <v>124286780</v>
       </c>
       <c r="B48" t="n">
-        <v>6672</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6675</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -6780,43 +6304,52 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124286781</v>
+        <v>126768713</v>
       </c>
       <c r="B49" t="n">
-        <v>5361</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8466</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>101728</v>
+        <v>101987</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Aspvedborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Heteroborips cryptographus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Ratzeburg, 1837)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6825,10 +6358,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628826</v>
+        <v>628893</v>
       </c>
       <c r="R49" t="n">
-        <v>6630334</v>
+        <v>6631195</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6865,7 +6398,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Färska puppkamrar (ingångshål tilltäppta med ljusa, grova vedspånor) i asphögstubbe, omkr. 137 cm.</t>
+          <t>Ca. 100 imago i och under barken på asplåga, omkr. 183 cm.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6879,7 +6412,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Äldre blandskog där granarna har dött.</t>
+          <t>Medelåldrig blandskog med överståndare.</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -6912,53 +6445,62 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124286778</v>
+        <v>24023085</v>
       </c>
       <c r="B50" t="n">
-        <v>80104</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57754</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228430</v>
+        <v>102118</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rostorangelav</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Blastenia ferruginea</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Huds.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+          <t>Degermossen, Skogstibble skjutfält, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>629196</v>
+        <v>628205</v>
       </c>
       <c r="R50" t="n">
-        <v>6630570</v>
+        <v>6631128</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>419</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6982,17 +6524,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>1978-06-04</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm.</t>
+          <t>1978-06-04</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7003,103 +6550,73 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>Äldre barr-/blandskog med mycket död gran.</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm. # Populus tremula</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Hasse Berglund</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Hasse Berglund</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126768713</v>
+        <v>21378974</v>
       </c>
       <c r="B51" t="n">
-        <v>8461</v>
+        <v>57942</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>101987</v>
+        <v>102119</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Aspvedborre</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Heteroborips cryptographus</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ratzeburg, 1837)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+          <t>Degermossen, Skogstibble skjutfält, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628893</v>
+        <v>628205</v>
       </c>
       <c r="R51" t="n">
-        <v>6631195</v>
+        <v>6631128</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>419</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7123,17 +6640,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>1987-05-19</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>1987-05-19</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ca. 100 imago i och under barken på asplåga, omkr. 183 cm.</t>
+          <t>NO om</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7144,39 +6671,1744 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>Medelåldrig blandskog med överståndare.</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
+          <t>Martin Tjernberg</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Martin Tjernberg</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>22365469</v>
+      </c>
+      <c r="B52" t="n">
+        <v>58607</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>102124</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vinterhämpling</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Linaria flavirostris</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Degermossen, Skogstibble skjutfält, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>628205</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6631128</v>
+      </c>
+      <c r="S52" t="n">
+        <v>419</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>1988-04-18</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>1988-04-18</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>norr om</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Martin Tjernberg</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Martin Tjernberg</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>31403224</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Degermossen, Skogstibble skjutfält, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>628205</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6631128</v>
+      </c>
+      <c r="S53" t="n">
+        <v>419</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2009-01-09</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2009-01-09</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Flög över vägen NO om Degermossen.</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Ulrik Lötberg</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Ulrik Lötberg</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>74631900</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>627641</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6630755</v>
+      </c>
+      <c r="S54" t="n">
+        <v>100</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>1997-10-09</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>1997-10-09</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>3-4 ex.</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
           <t>Gillis Aronsson</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
+      <c r="AX54" t="inlineStr">
         <is>
           <t>Gillis Aronsson</t>
         </is>
       </c>
-      <c r="AY51" t="inlineStr"/>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>18401685</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Degermossen, Skogstibble skjutfält, Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>628205</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6631128</v>
+      </c>
+      <c r="S55" t="n">
+        <v>419</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2003-03-23</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2003-03-23</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Erik Landgren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Erik Landgren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>19230547</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57794</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Degermossen, Skogstibble skjutfält, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>628205</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6631128</v>
+      </c>
+      <c r="S56" t="n">
+        <v>419</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2003-03-29</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2003-03-29</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>söder degermossen</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Pekka Westin</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Pekka Westin</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>44285995</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57785</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>102622</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Pärluggla</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Aegolius funereus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Degermossen, Skogstibble skjutfält, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>628205</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6631128</v>
+      </c>
+      <c r="S57" t="n">
+        <v>419</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>1999-03-14</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>03:40</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>1999-03-14</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Avlyssnas från Stora Kokärr. Hörs tydligt i riktning mot södra delen av Degermossen kl 04:30 och 04:40. Samma individ som tidigare på morgonen?</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Martin Tjernberg</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Martin Tjernberg</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>20654665</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Degermossen, Skogstibble skjutfält, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>628205</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6631128</v>
+      </c>
+      <c r="S58" t="n">
+        <v>419</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2005-02-06</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2005-02-06</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Martin Tjernberg</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Martin Tjernberg</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>23241383</v>
+      </c>
+      <c r="B59" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Degermossen, Skogstibble skjutfält, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>628205</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6631128</v>
+      </c>
+      <c r="S59" t="n">
+        <v>419</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2006-04-14</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2006-04-14</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Stefan Larsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Stefan Larsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>37858858</v>
+      </c>
+      <c r="B60" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Degermossen, Skogstibble skjutfält, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>628205</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6631128</v>
+      </c>
+      <c r="S60" t="n">
+        <v>419</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2011-01-15</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2011-01-15</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Yngve Hareland</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Yngve Hareland, Lotta Hedkvist</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>37859799</v>
+      </c>
+      <c r="B61" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Degermossen, Skogstibble skjutfält, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>628205</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6631128</v>
+      </c>
+      <c r="S61" t="n">
+        <v>419</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2011-01-15</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2011-01-15</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Yngve Hareland</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Yngve Hareland, Lotta Hedkvist</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>65889562</v>
+      </c>
+      <c r="B62" t="n">
+        <v>102302</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221223</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vippärt</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lathyrus niger</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble skjutfält, 200 m NO om Björnkällan, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>628502</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6630221</v>
+      </c>
+      <c r="S62" t="n">
+        <v>100</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2003-01-01</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2003-12-31</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter. Observatör Per Kornhall</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Via Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>74741293</v>
+      </c>
+      <c r="B63" t="n">
+        <v>102225</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>221223</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vippärt</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Lathyrus niger</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>628744</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6630468</v>
+      </c>
+      <c r="S63" t="n">
+        <v>50</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>1997-09-01</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>1997-09-01</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Några plantor i ett aspbestånd.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>124286770</v>
+      </c>
+      <c r="B64" t="n">
+        <v>80657</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>228430</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Blastenia relicta</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Arup &amp; Vondrák</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>628939</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6631046</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm.</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Medelåldrig blandskog med överståndare.</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Bark på centimetertjock gren i avbruten topp från levande asp, omkr. 156 cm. # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>124286778</v>
+      </c>
+      <c r="B65" t="n">
+        <v>80657</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>228430</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Blastenia relicta</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Arup &amp; Vondrák</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>629196</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6630570</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm.</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Äldre barr-/blandskog med mycket död gran.</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Bark på centimetertjock gren i kronan av asplåga, omkr. 95 cm. # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>74811572</v>
+      </c>
+      <c r="B66" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>627841</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6630698</v>
+      </c>
+      <c r="S66" t="n">
+        <v>25</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>1997-08-31</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>1997-08-31</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På stammen av levande asp, omkr. 164 cm.</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL66" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Stammen av levande asp. # Asp</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
